--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Midcap 150 ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Midcap 150 ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="386">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Midcap 150 ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,6 +61,24 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>BSE Ltd.</t>
+  </si>
+  <si>
+    <t>INE118H01025</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Suzlon Energy Ltd.</t>
+  </si>
+  <si>
+    <t>INE040H01021</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
     <t>MAX Healthcare Institute Ltd</t>
   </si>
   <si>
@@ -70,292 +88,409 @@
     <t>Healthcare Services</t>
   </si>
   <si>
-    <t>BSE Ltd.</t>
-  </si>
-  <si>
-    <t>INE118H01025</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Suzlon Energy Ltd.</t>
-  </si>
-  <si>
-    <t>INE040H01021</t>
-  </si>
-  <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
-    <t>The Indian Hotels Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE053A01029</t>
+    <t>Persistent Systems Ltd.</t>
+  </si>
+  <si>
+    <t>INE262H01021</t>
+  </si>
+  <si>
+    <t>It - Software</t>
+  </si>
+  <si>
+    <t>PB Fintech Ltd.</t>
+  </si>
+  <si>
+    <t>INE417T01026</t>
+  </si>
+  <si>
+    <t>Financial Technology (Fintech)</t>
+  </si>
+  <si>
+    <t>COFORGE Ltd.</t>
+  </si>
+  <si>
+    <t>INE591G01017</t>
+  </si>
+  <si>
+    <t>Dixon Technologies (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE935N01020</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Indus Towers Ltd.</t>
+  </si>
+  <si>
+    <t>INE121J01017</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
+    <t>The Federal Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE171A01029</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>HDFC Asset Management Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE127D01025</t>
+  </si>
+  <si>
+    <t>Lupin Ltd.</t>
+  </si>
+  <si>
+    <t>INE326A01037</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>IDFC First Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE092T01019</t>
+  </si>
+  <si>
+    <t>SRF Ltd.</t>
+  </si>
+  <si>
+    <t>INE647A01010</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
+    <t>Yes Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE528G01035</t>
+  </si>
+  <si>
+    <t>Hindustan Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE094A01015</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>Solar Industries India Ltd.</t>
+  </si>
+  <si>
+    <t>INE343H01029</t>
+  </si>
+  <si>
+    <t>AU Small Finance Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE949L01017</t>
+  </si>
+  <si>
+    <t>Max Financial Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE180A01020</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Marico Ltd.</t>
+  </si>
+  <si>
+    <t>INE196A01026</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
+  </si>
+  <si>
+    <t>Fortis Healthcare Ltd.</t>
+  </si>
+  <si>
+    <t>INE061F01013</t>
+  </si>
+  <si>
+    <t>Sundaram Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE660A01013</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Godrej Properties Ltd.</t>
+  </si>
+  <si>
+    <t>INE484J01027</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
+    <t>Ashok Leyland Ltd.</t>
+  </si>
+  <si>
+    <t>INE208A01029</t>
+  </si>
+  <si>
+    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
+  </si>
+  <si>
+    <t>Bharat Heavy Electricals Ltd.</t>
+  </si>
+  <si>
+    <t>INE257A01026</t>
+  </si>
+  <si>
+    <t>Bharat Forge Ltd.</t>
+  </si>
+  <si>
+    <t>INE465A01025</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Tube Investments of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE974X01010</t>
+  </si>
+  <si>
+    <t>APL Apollo Tubes Ltd.</t>
+  </si>
+  <si>
+    <t>INE702C01027</t>
+  </si>
+  <si>
+    <t>Colgate - Palmolive (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE259A01022</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Aurobindo Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE406A01037</t>
+  </si>
+  <si>
+    <t>UPL Ltd.</t>
+  </si>
+  <si>
+    <t>INE628A01036</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agrochemicals</t>
+  </si>
+  <si>
+    <t>PI Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE603J01030</t>
+  </si>
+  <si>
+    <t>One 97 Communications Ltd</t>
+  </si>
+  <si>
+    <t>INE982J01020</t>
+  </si>
+  <si>
+    <t>Polycab India Ltd.</t>
+  </si>
+  <si>
+    <t>INE455K01017</t>
+  </si>
+  <si>
+    <t>Gmr Airports Ltd.</t>
+  </si>
+  <si>
+    <t>INE776C01039</t>
+  </si>
+  <si>
+    <t>Transport Infrastructure</t>
+  </si>
+  <si>
+    <t>Page Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE761H01022</t>
+  </si>
+  <si>
+    <t>Textiles &amp; Apparels</t>
+  </si>
+  <si>
+    <t>Mphasis Ltd.</t>
+  </si>
+  <si>
+    <t>INE356A01018</t>
+  </si>
+  <si>
+    <t>Voltas Ltd.</t>
+  </si>
+  <si>
+    <t>INE226A01021</t>
+  </si>
+  <si>
+    <t>The Phoenix Mills Ltd.</t>
+  </si>
+  <si>
+    <t>INE211B01039</t>
+  </si>
+  <si>
+    <t>Union Bank Of India</t>
+  </si>
+  <si>
+    <t>INE692A01016</t>
+  </si>
+  <si>
+    <t>MRF Ltd.</t>
+  </si>
+  <si>
+    <t>INE883A01011</t>
+  </si>
+  <si>
+    <t>Mankind Pharma Ltd</t>
+  </si>
+  <si>
+    <t>INE634S01028</t>
+  </si>
+  <si>
+    <t>Ge Vernova T&amp;D India Ltd.</t>
+  </si>
+  <si>
+    <t>INE200A01026</t>
+  </si>
+  <si>
+    <t>FSN E-Commerce Ventures Ltd.</t>
+  </si>
+  <si>
+    <t>INE388Y01029</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
+    <t>NHPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE848E01016</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>SBI Cards &amp; Payment Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE018E01016</t>
+  </si>
+  <si>
+    <t>Alkem Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE540L01014</t>
+  </si>
+  <si>
+    <t>Coromandel International Ltd.</t>
+  </si>
+  <si>
+    <t>INE169A01031</t>
+  </si>
+  <si>
+    <t>Supreme Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE195A01028</t>
+  </si>
+  <si>
+    <t>Torrent Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE813H01021</t>
+  </si>
+  <si>
+    <t>Jubilant Foodworks Ltd.</t>
+  </si>
+  <si>
+    <t>INE797F01020</t>
   </si>
   <si>
     <t>Leisure Services</t>
   </si>
   <si>
-    <t>Persistent Systems Ltd.</t>
-  </si>
-  <si>
-    <t>INE262H01021</t>
-  </si>
-  <si>
-    <t>It - Software</t>
-  </si>
-  <si>
-    <t>Dixon Technologies (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE935N01020</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>PB Fintech Ltd.</t>
-  </si>
-  <si>
-    <t>INE417T01026</t>
-  </si>
-  <si>
-    <t>Financial Technology (Fintech)</t>
-  </si>
-  <si>
-    <t>COFORGE Ltd.</t>
-  </si>
-  <si>
-    <t>INE591G01017</t>
-  </si>
-  <si>
-    <t>Lupin Ltd.</t>
-  </si>
-  <si>
-    <t>INE326A01037</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
-  </si>
-  <si>
-    <t>The Federal Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE171A01029</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>Indus Towers Ltd.</t>
-  </si>
-  <si>
-    <t>INE121J01017</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>SRF Ltd.</t>
-  </si>
-  <si>
-    <t>INE647A01010</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>CG Power and Industrial Solutions Ltd.</t>
-  </si>
-  <si>
-    <t>INE067A01029</t>
-  </si>
-  <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>HDFC Asset Management Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE127D01025</t>
-  </si>
-  <si>
-    <t>IDFC First Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE092T01019</t>
-  </si>
-  <si>
-    <t>Colgate - Palmolive (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE259A01022</t>
-  </si>
-  <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
-    <t>Yes Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE528G01035</t>
-  </si>
-  <si>
-    <t>Tube Investments of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE974X01010</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Marico Ltd.</t>
-  </si>
-  <si>
-    <t>INE196A01026</t>
-  </si>
-  <si>
-    <t>Agricultural Food &amp; Other Products</t>
-  </si>
-  <si>
-    <t>Godrej Properties Ltd.</t>
-  </si>
-  <si>
-    <t>INE484J01027</t>
-  </si>
-  <si>
-    <t>Realty</t>
-  </si>
-  <si>
-    <t>Hindustan Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE094A01015</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>AU Small Finance Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE949L01017</t>
-  </si>
-  <si>
-    <t>Fortis Healthcare Ltd.</t>
-  </si>
-  <si>
-    <t>INE061F01013</t>
-  </si>
-  <si>
-    <t>Aurobindo Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE406A01037</t>
-  </si>
-  <si>
-    <t>Mphasis Ltd.</t>
-  </si>
-  <si>
-    <t>INE356A01018</t>
-  </si>
-  <si>
-    <t>Bharat Forge Ltd.</t>
-  </si>
-  <si>
-    <t>INE465A01025</t>
-  </si>
-  <si>
-    <t>Sundaram Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE660A01013</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Ashok Leyland Ltd.</t>
-  </si>
-  <si>
-    <t>INE208A01029</t>
-  </si>
-  <si>
-    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
-  </si>
-  <si>
-    <t>The Phoenix Mills Ltd.</t>
-  </si>
-  <si>
-    <t>INE211B01039</t>
-  </si>
-  <si>
-    <t>UPL Ltd.</t>
-  </si>
-  <si>
-    <t>INE628A01036</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Polycab India Ltd.</t>
-  </si>
-  <si>
-    <t>INE455K01017</t>
-  </si>
-  <si>
-    <t>Voltas Ltd.</t>
-  </si>
-  <si>
-    <t>INE226A01021</t>
-  </si>
-  <si>
-    <t>Max Financial Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE180A01020</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>PI Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE603J01030</t>
-  </si>
-  <si>
-    <t>Page Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE761H01022</t>
-  </si>
-  <si>
-    <t>Textiles &amp; Apparels</t>
-  </si>
-  <si>
-    <t>Torrent Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE813H01021</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>APL Apollo Tubes Ltd.</t>
-  </si>
-  <si>
-    <t>INE702C01027</t>
+    <t>Prestige Estates Projects Ltd.</t>
+  </si>
+  <si>
+    <t>INE811K01011</t>
+  </si>
+  <si>
+    <t>NMDC Ltd.</t>
+  </si>
+  <si>
+    <t>INE584A01023</t>
+  </si>
+  <si>
+    <t>Minerals &amp; Mining</t>
+  </si>
+  <si>
+    <t>Hitachi Energy India Ltd.</t>
+  </si>
+  <si>
+    <t>INE07Y701011</t>
+  </si>
+  <si>
+    <t>Sona Blw Precision Forgings Ltd.</t>
+  </si>
+  <si>
+    <t>INE073K01018</t>
+  </si>
+  <si>
+    <t>Muthoot Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE414G01012</t>
+  </si>
+  <si>
+    <t>Oil India Ltd.</t>
+  </si>
+  <si>
+    <t>INE274J01014</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Petronet LNG Ltd.</t>
+  </si>
+  <si>
+    <t>INE347G01014</t>
+  </si>
+  <si>
+    <t>Gas</t>
   </si>
   <si>
     <t>Rail Vikas Nigam Ltd.</t>
@@ -367,49 +502,25 @@
     <t>Construction</t>
   </si>
   <si>
-    <t>Alkem Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE540L01014</t>
-  </si>
-  <si>
-    <t>Jubilant Foodworks Ltd.</t>
-  </si>
-  <si>
-    <t>INE797F01020</t>
-  </si>
-  <si>
-    <t>One 97 Communications Ltd</t>
-  </si>
-  <si>
-    <t>INE982J01020</t>
-  </si>
-  <si>
-    <t>Gmr Airports Ltd.</t>
-  </si>
-  <si>
-    <t>INE776C01039</t>
-  </si>
-  <si>
-    <t>Transport Infrastructure</t>
-  </si>
-  <si>
-    <t>Supreme Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE195A01028</t>
-  </si>
-  <si>
-    <t>Mankind Pharma Ltd</t>
-  </si>
-  <si>
-    <t>INE634S01028</t>
-  </si>
-  <si>
-    <t>Solar Industries India Ltd.</t>
-  </si>
-  <si>
-    <t>INE343H01029</t>
+    <t>JK Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE823G01014</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Indian Railway Catering and Tourism Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE335Y01020</t>
+  </si>
+  <si>
+    <t>Tata Elxsi Ltd.</t>
+  </si>
+  <si>
+    <t>INE670A01012</t>
   </si>
   <si>
     <t>KEI Industries Ltd.</t>
@@ -418,19 +529,91 @@
     <t>INE878B01027</t>
   </si>
   <si>
-    <t>Muthoot Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE414G01012</t>
-  </si>
-  <si>
-    <t>Petronet LNG Ltd.</t>
-  </si>
-  <si>
-    <t>INE347G01014</t>
-  </si>
-  <si>
-    <t>Gas</t>
+    <t>Glenmark Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE935A01035</t>
+  </si>
+  <si>
+    <t>KPIT Technologies Ltd</t>
+  </si>
+  <si>
+    <t>INE04I401011</t>
+  </si>
+  <si>
+    <t>Indian Bank</t>
+  </si>
+  <si>
+    <t>INE562A01011</t>
+  </si>
+  <si>
+    <t>Container Corporation Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE111A01025</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>Kalyan Jewellers India Ltd.</t>
+  </si>
+  <si>
+    <t>INE303R01014</t>
+  </si>
+  <si>
+    <t>Mazagon Dock Shipbuilders Ltd</t>
+  </si>
+  <si>
+    <t>INE249Z01020</t>
+  </si>
+  <si>
+    <t>Industrial Manufacturing</t>
+  </si>
+  <si>
+    <t>Jindal Stainless Ltd.</t>
+  </si>
+  <si>
+    <t>INE220G01021</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Oberoi Realty Ltd.</t>
+  </si>
+  <si>
+    <t>INE093I01010</t>
+  </si>
+  <si>
+    <t>Oracle Financial Services Software Ltd.</t>
+  </si>
+  <si>
+    <t>INE881D01027</t>
+  </si>
+  <si>
+    <t>Blue Star Ltd.</t>
+  </si>
+  <si>
+    <t>INE472A01039</t>
+  </si>
+  <si>
+    <t>IPCA Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE571A01038</t>
+  </si>
+  <si>
+    <t>Balkrishna Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE787D01026</t>
+  </si>
+  <si>
+    <t>Tata Communications Ltd.</t>
+  </si>
+  <si>
+    <t>INE151A01013</t>
   </si>
   <si>
     <t>Vodafone Idea Ltd.</t>
@@ -439,118 +622,25 @@
     <t>INE669E01016</t>
   </si>
   <si>
-    <t>SBI Cards &amp; Payment Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE018E01016</t>
-  </si>
-  <si>
-    <t>MRF Ltd.</t>
-  </si>
-  <si>
-    <t>INE883A01011</t>
-  </si>
-  <si>
-    <t>FSN E-Commerce Ventures Ltd.</t>
-  </si>
-  <si>
-    <t>INE388Y01029</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
-    <t>KPIT Technologies Ltd</t>
-  </si>
-  <si>
-    <t>INE04I401011</t>
-  </si>
-  <si>
-    <t>Prestige Estates Projects Ltd.</t>
-  </si>
-  <si>
-    <t>INE811K01011</t>
-  </si>
-  <si>
-    <t>Oil India Ltd.</t>
-  </si>
-  <si>
-    <t>INE274J01014</t>
-  </si>
-  <si>
-    <t>Oil</t>
-  </si>
-  <si>
-    <t>NMDC Ltd.</t>
-  </si>
-  <si>
-    <t>INE584A01023</t>
-  </si>
-  <si>
-    <t>Minerals &amp; Mining</t>
-  </si>
-  <si>
-    <t>Sona Blw Precision Forgings Ltd.</t>
-  </si>
-  <si>
-    <t>INE073K01018</t>
-  </si>
-  <si>
-    <t>Balkrishna Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE787D01026</t>
-  </si>
-  <si>
-    <t>Tata Elxsi Ltd.</t>
-  </si>
-  <si>
-    <t>INE670A01012</t>
-  </si>
-  <si>
-    <t>Oracle Financial Services Software Ltd.</t>
-  </si>
-  <si>
-    <t>INE881D01027</t>
-  </si>
-  <si>
-    <t>Container Corporation Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE111A01025</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>Oberoi Realty Ltd.</t>
-  </si>
-  <si>
-    <t>INE093I01010</t>
-  </si>
-  <si>
-    <t>Jindal Stainless Ltd.</t>
-  </si>
-  <si>
-    <t>INE220G01021</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Coromandel International Ltd.</t>
-  </si>
-  <si>
-    <t>INE169A01031</t>
-  </si>
-  <si>
-    <t>JK Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE823G01014</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
+    <t>Adani total gas Ltd.</t>
+  </si>
+  <si>
+    <t>INE399L01023</t>
+  </si>
+  <si>
+    <t>Steel Authority Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE114A01011</t>
+  </si>
+  <si>
+    <t>Bharat Dynamics Ltd.</t>
+  </si>
+  <si>
+    <t>INE171Z01026</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
   </si>
   <si>
     <t>Patanjali Foods Ltd.</t>
@@ -559,36 +649,18 @@
     <t>INE619A01035</t>
   </si>
   <si>
-    <t>Indian Bank</t>
-  </si>
-  <si>
-    <t>INE562A01011</t>
-  </si>
-  <si>
-    <t>IPCA Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE571A01038</t>
-  </si>
-  <si>
-    <t>Kalyan Jewellers India Ltd.</t>
-  </si>
-  <si>
-    <t>INE303R01014</t>
-  </si>
-  <si>
-    <t>Tata Communications Ltd.</t>
-  </si>
-  <si>
-    <t>INE151A01013</t>
-  </si>
-  <si>
     <t>Astral Ltd.</t>
   </si>
   <si>
     <t>INE006I01046</t>
   </si>
   <si>
+    <t>UNO Minda Ltd.</t>
+  </si>
+  <si>
+    <t>INE405E01023</t>
+  </si>
+  <si>
     <t>LIC Housing Finance Ltd.</t>
   </si>
   <si>
@@ -601,22 +673,85 @@
     <t>INE302A01020</t>
   </si>
   <si>
-    <t>UNO Minda Ltd.</t>
-  </si>
-  <si>
-    <t>INE405E01023</t>
-  </si>
-  <si>
     <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
   </si>
   <si>
     <t>INE774D01024</t>
   </si>
   <si>
-    <t>Delhivery Ltd.</t>
-  </si>
-  <si>
-    <t>INE148O01028</t>
+    <t>Lloyds Metals &amp; Energy Ltd.</t>
+  </si>
+  <si>
+    <t>INE281B01032</t>
+  </si>
+  <si>
+    <t>Schaeffler India Ltd.</t>
+  </si>
+  <si>
+    <t>INE513A01022</t>
+  </si>
+  <si>
+    <t>Hindustan Zinc Ltd.</t>
+  </si>
+  <si>
+    <t>INE267A01025</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Cochin Shipyard Ltd.</t>
+  </si>
+  <si>
+    <t>INE704P01025</t>
+  </si>
+  <si>
+    <t>Berger Paints India Ltd.</t>
+  </si>
+  <si>
+    <t>INE463A01038</t>
+  </si>
+  <si>
+    <t>National Aluminium Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE139A01034</t>
+  </si>
+  <si>
+    <t>Dalmia Bharat Ltd.</t>
+  </si>
+  <si>
+    <t>INE00R701025</t>
+  </si>
+  <si>
+    <t>360 One Wam Ltd.</t>
+  </si>
+  <si>
+    <t>INE466L01038</t>
+  </si>
+  <si>
+    <t>Aditya Birla Capital Ltd.</t>
+  </si>
+  <si>
+    <t>INE674K01013</t>
+  </si>
+  <si>
+    <t>Abbott India Ltd.</t>
+  </si>
+  <si>
+    <t>INE358A01014</t>
+  </si>
+  <si>
+    <t>Linde India Ltd.</t>
+  </si>
+  <si>
+    <t>INE473A01011</t>
+  </si>
+  <si>
+    <t>Apollo Tyres Ltd.</t>
+  </si>
+  <si>
+    <t>INE438A01022</t>
   </si>
   <si>
     <t>Biocon Ltd.</t>
@@ -625,6 +760,24 @@
     <t>INE376G01013</t>
   </si>
   <si>
+    <t>Bank Of India</t>
+  </si>
+  <si>
+    <t>INE084A01016</t>
+  </si>
+  <si>
+    <t>Gujarat Fluorochemicals Ltd.</t>
+  </si>
+  <si>
+    <t>INE09N301011</t>
+  </si>
+  <si>
+    <t>Indraprastha Gas Ltd.</t>
+  </si>
+  <si>
+    <t>INE203G01027</t>
+  </si>
+  <si>
     <t>United Breweries Ltd.</t>
   </si>
   <si>
@@ -634,37 +787,46 @@
     <t>Beverages</t>
   </si>
   <si>
+    <t>Bandhan Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE545U01014</t>
+  </si>
+  <si>
     <t>Deepak Nitrite Ltd.</t>
   </si>
   <si>
     <t>INE288B01029</t>
   </si>
   <si>
-    <t>Steel Authority Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE114A01011</t>
-  </si>
-  <si>
-    <t>Tata Chemicals Ltd.</t>
-  </si>
-  <si>
-    <t>INE092A01019</t>
-  </si>
-  <si>
-    <t>Mazagon Dock Shipbuilders Ltd</t>
-  </si>
-  <si>
-    <t>INE249Z01020</t>
-  </si>
-  <si>
-    <t>Industrial Manufacturing</t>
-  </si>
-  <si>
-    <t>Lloyds Metals &amp; Energy Ltd.</t>
-  </si>
-  <si>
-    <t>INE281B01032</t>
+    <t>Bharti Hexacom Ltd.</t>
+  </si>
+  <si>
+    <t>INE343G01021</t>
+  </si>
+  <si>
+    <t>L&amp;T Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE498L01015</t>
+  </si>
+  <si>
+    <t>Apar Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE372A01015</t>
+  </si>
+  <si>
+    <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE159A01016</t>
+  </si>
+  <si>
+    <t>AIA Engineering Ltd.</t>
+  </si>
+  <si>
+    <t>INE212H01026</t>
   </si>
   <si>
     <t>Thermax Ltd.</t>
@@ -673,6 +835,54 @@
     <t>INE152A01029</t>
   </si>
   <si>
+    <t>Nippon Life India Asset Management Ltd</t>
+  </si>
+  <si>
+    <t>INE298J01013</t>
+  </si>
+  <si>
+    <t>CRISIL Ltd.</t>
+  </si>
+  <si>
+    <t>INE007A01025</t>
+  </si>
+  <si>
+    <t>General Insurance Corporation of India</t>
+  </si>
+  <si>
+    <t>INE481Y01014</t>
+  </si>
+  <si>
+    <t>ACC Ltd.</t>
+  </si>
+  <si>
+    <t>INE012A01025</t>
+  </si>
+  <si>
+    <t>Gland Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE068V01023</t>
+  </si>
+  <si>
+    <t>Syngene International Ltd.</t>
+  </si>
+  <si>
+    <t>INE398R01022</t>
+  </si>
+  <si>
+    <t>Housing &amp; Urban Development Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE031A01017</t>
+  </si>
+  <si>
+    <t>Motilal Oswal Financial Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE338I01027</t>
+  </si>
+  <si>
     <t>L&amp;T Technology Services Ltd.</t>
   </si>
   <si>
@@ -682,64 +892,10 @@
     <t>It - Services</t>
   </si>
   <si>
-    <t>Dalmia Bharat Ltd.</t>
-  </si>
-  <si>
-    <t>INE00R701025</t>
-  </si>
-  <si>
-    <t>Gujarat Fluorochemicals Ltd.</t>
-  </si>
-  <si>
-    <t>INE09N301011</t>
-  </si>
-  <si>
-    <t>Apollo Tyres Ltd.</t>
-  </si>
-  <si>
-    <t>INE438A01022</t>
-  </si>
-  <si>
-    <t>AIA Engineering Ltd.</t>
-  </si>
-  <si>
-    <t>INE212H01026</t>
-  </si>
-  <si>
-    <t>Indraprastha Gas Ltd.</t>
-  </si>
-  <si>
-    <t>INE203G01027</t>
-  </si>
-  <si>
-    <t>Schaeffler India Ltd.</t>
-  </si>
-  <si>
-    <t>INE513A01022</t>
-  </si>
-  <si>
-    <t>Procter &amp; Gamble Hygiene and Health Care Ltd.</t>
-  </si>
-  <si>
-    <t>INE179A01014</t>
-  </si>
-  <si>
-    <t>Bank Of India</t>
-  </si>
-  <si>
-    <t>INE084A01016</t>
-  </si>
-  <si>
-    <t>ACC Ltd.</t>
-  </si>
-  <si>
-    <t>INE012A01025</t>
-  </si>
-  <si>
-    <t>Abbott India Ltd.</t>
-  </si>
-  <si>
-    <t>INE358A01014</t>
+    <t>Tata Technologies Ltd</t>
+  </si>
+  <si>
+    <t>INE142M01025</t>
   </si>
   <si>
     <t>Indian Renewable Energy Development Agency Ltd</t>
@@ -748,85 +904,16 @@
     <t>INE202E01016</t>
   </si>
   <si>
-    <t>Hitachi Energy India Ltd.</t>
-  </si>
-  <si>
-    <t>INE07Y701011</t>
-  </si>
-  <si>
-    <t>Syngene International Ltd.</t>
-  </si>
-  <si>
-    <t>INE398R01022</t>
-  </si>
-  <si>
-    <t>Berger Paints India Ltd.</t>
-  </si>
-  <si>
-    <t>INE463A01038</t>
-  </si>
-  <si>
-    <t>Hindustan Zinc Ltd.</t>
-  </si>
-  <si>
-    <t>INE267A01025</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>CRISIL Ltd.</t>
-  </si>
-  <si>
-    <t>INE007A01025</t>
-  </si>
-  <si>
-    <t>Carborundum Universal Ltd.</t>
-  </si>
-  <si>
-    <t>INE120A01034</t>
-  </si>
-  <si>
-    <t>Linde India Ltd.</t>
-  </si>
-  <si>
-    <t>INE473A01011</t>
-  </si>
-  <si>
-    <t>Cochin Shipyard Ltd.</t>
-  </si>
-  <si>
-    <t>INE704P01025</t>
-  </si>
-  <si>
-    <t>Aditya Birla Capital Ltd.</t>
-  </si>
-  <si>
-    <t>INE674K01013</t>
-  </si>
-  <si>
-    <t>General Insurance Corporation of India</t>
-  </si>
-  <si>
-    <t>INE481Y01014</t>
-  </si>
-  <si>
-    <t>Bandhan Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE545U01014</t>
-  </si>
-  <si>
-    <t>Tata Technologies Ltd</t>
-  </si>
-  <si>
-    <t>INE142M01025</t>
-  </si>
-  <si>
-    <t>Gland Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE068V01023</t>
+    <t>Emami Ltd.</t>
+  </si>
+  <si>
+    <t>INE548C01032</t>
+  </si>
+  <si>
+    <t>K.P.R. Mill Ltd.</t>
+  </si>
+  <si>
+    <t>INE930H01031</t>
   </si>
   <si>
     <t>Escorts Kubota Ltd</t>
@@ -835,19 +922,157 @@
     <t>INE042A01014</t>
   </si>
   <si>
-    <t>Bharat Dynamics Ltd.</t>
-  </si>
-  <si>
-    <t>INE171Z01026</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
-    <t>L&amp;T Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE498L01015</t>
+    <t>Star Health &amp; Allied Insurance</t>
+  </si>
+  <si>
+    <t>INE575P01011</t>
+  </si>
+  <si>
+    <t>Ajanta Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE031B01049</t>
+  </si>
+  <si>
+    <t>IRB Infrastructure Developers Ltd.</t>
+  </si>
+  <si>
+    <t>INE821I01022</t>
+  </si>
+  <si>
+    <t>Global Health Ltd</t>
+  </si>
+  <si>
+    <t>INE474Q01031</t>
+  </si>
+  <si>
+    <t>Motherson Sumi Wiring India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0FS801015</t>
+  </si>
+  <si>
+    <t>Vishal Mega Mart Ltd.</t>
+  </si>
+  <si>
+    <t>INE01EA01019</t>
+  </si>
+  <si>
+    <t>Adani Wilmar Ltd</t>
+  </si>
+  <si>
+    <t>INE699H01024</t>
+  </si>
+  <si>
+    <t>Tata Investment Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE672A01018</t>
+  </si>
+  <si>
+    <t>Endurance Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE913H01037</t>
+  </si>
+  <si>
+    <t>Bank Of Maharashtra</t>
+  </si>
+  <si>
+    <t>INE457A01014</t>
+  </si>
+  <si>
+    <t>Honeywell Automation India Ltd.</t>
+  </si>
+  <si>
+    <t>INE671A01010</t>
+  </si>
+  <si>
+    <t>NTPC Green Energy Ltd</t>
+  </si>
+  <si>
+    <t>INE0ONG01011</t>
+  </si>
+  <si>
+    <t>3M India Ltd.</t>
+  </si>
+  <si>
+    <t>INE470A01017</t>
+  </si>
+  <si>
+    <t>Diversified</t>
+  </si>
+  <si>
+    <t>Aditya Birla Lifestyle Brands Ltd.</t>
+  </si>
+  <si>
+    <t>INE14LE01019</t>
+  </si>
+  <si>
+    <t>Gujarat Gas Ltd.</t>
+  </si>
+  <si>
+    <t>INE844O01030</t>
+  </si>
+  <si>
+    <t>JSW Infrastructure Ltd</t>
+  </si>
+  <si>
+    <t>INE880J01026</t>
+  </si>
+  <si>
+    <t>NLC India Ltd.</t>
+  </si>
+  <si>
+    <t>INE589A01014</t>
+  </si>
+  <si>
+    <t>WAAREE Energies Ltd</t>
+  </si>
+  <si>
+    <t>INE377N01017</t>
+  </si>
+  <si>
+    <t>Godrej Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE233A01035</t>
+  </si>
+  <si>
+    <t>Premier Energies Ltd.</t>
+  </si>
+  <si>
+    <t>INE0BS701011</t>
+  </si>
+  <si>
+    <t>SJVN Ltd.</t>
+  </si>
+  <si>
+    <t>INE002L01015</t>
+  </si>
+  <si>
+    <t>Sun TV Network Ltd.</t>
+  </si>
+  <si>
+    <t>INE424H01027</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Ola Electric Mobility Ltd.</t>
+  </si>
+  <si>
+    <t>INE0LXG01040</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>The New India Assurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE470Y01017</t>
   </si>
   <si>
     <t>Aditya Birla Fashion and Retail Ltd.</t>
@@ -856,222 +1081,6 @@
     <t>INE647O01011</t>
   </si>
   <si>
-    <t>Emami Ltd.</t>
-  </si>
-  <si>
-    <t>INE548C01032</t>
-  </si>
-  <si>
-    <t>Sundram Fasteners Ltd.</t>
-  </si>
-  <si>
-    <t>INE387A01021</t>
-  </si>
-  <si>
-    <t>Housing &amp; Urban Development Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE031A01017</t>
-  </si>
-  <si>
-    <t>IRB Infrastructure Developers Ltd.</t>
-  </si>
-  <si>
-    <t>INE821I01022</t>
-  </si>
-  <si>
-    <t>Ajanta Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE031B01049</t>
-  </si>
-  <si>
-    <t>Timken India Ltd.</t>
-  </si>
-  <si>
-    <t>INE325A01013</t>
-  </si>
-  <si>
-    <t>Bharti Hexacom Ltd.</t>
-  </si>
-  <si>
-    <t>INE343G01021</t>
-  </si>
-  <si>
-    <t>Nippon Life India Asset Management Ltd</t>
-  </si>
-  <si>
-    <t>INE298J01013</t>
-  </si>
-  <si>
-    <t>Star Health &amp; Allied Insurance</t>
-  </si>
-  <si>
-    <t>INE575P01011</t>
-  </si>
-  <si>
-    <t>Motherson Sumi Wiring India Ltd.</t>
-  </si>
-  <si>
-    <t>INE0FS801015</t>
-  </si>
-  <si>
-    <t>SKF India Ltd.</t>
-  </si>
-  <si>
-    <t>INE640A01023</t>
-  </si>
-  <si>
-    <t>K.P.R. Mill Ltd.</t>
-  </si>
-  <si>
-    <t>INE930H01031</t>
-  </si>
-  <si>
-    <t>Poonawalla Fincorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE511C01022</t>
-  </si>
-  <si>
-    <t>Grindwell Norton Ltd.</t>
-  </si>
-  <si>
-    <t>INE536A01023</t>
-  </si>
-  <si>
-    <t>Honeywell Automation India Ltd.</t>
-  </si>
-  <si>
-    <t>INE671A01010</t>
-  </si>
-  <si>
-    <t>Global Health Ltd</t>
-  </si>
-  <si>
-    <t>INE474Q01031</t>
-  </si>
-  <si>
-    <t>3M India Ltd.</t>
-  </si>
-  <si>
-    <t>INE470A01017</t>
-  </si>
-  <si>
-    <t>Diversified</t>
-  </si>
-  <si>
-    <t>Gujarat Gas Ltd.</t>
-  </si>
-  <si>
-    <t>INE844O01030</t>
-  </si>
-  <si>
-    <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE159A01016</t>
-  </si>
-  <si>
-    <t>Bank Of Maharashtra</t>
-  </si>
-  <si>
-    <t>INE457A01014</t>
-  </si>
-  <si>
-    <t>Tata Investment Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE672A01018</t>
-  </si>
-  <si>
-    <t>JSW Infrastructure Ltd</t>
-  </si>
-  <si>
-    <t>INE880J01026</t>
-  </si>
-  <si>
-    <t>NLC India Ltd.</t>
-  </si>
-  <si>
-    <t>INE589A01014</t>
-  </si>
-  <si>
-    <t>Endurance Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE913H01037</t>
-  </si>
-  <si>
-    <t>SJVN Ltd.</t>
-  </si>
-  <si>
-    <t>INE002L01015</t>
-  </si>
-  <si>
-    <t>ZF Commercial Vehicle Control Systems India Ltd</t>
-  </si>
-  <si>
-    <t>INE342J01019</t>
-  </si>
-  <si>
-    <t>Bayer Cropscience Ltd.</t>
-  </si>
-  <si>
-    <t>INE462A01022</t>
-  </si>
-  <si>
-    <t>The Fertilisers and Chemicals.</t>
-  </si>
-  <si>
-    <t>INE188A01015</t>
-  </si>
-  <si>
-    <t>Godrej Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE233A01035</t>
-  </si>
-  <si>
-    <t>Sun TV Network Ltd.</t>
-  </si>
-  <si>
-    <t>INE424H01027</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>IDBI Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE008A01015</t>
-  </si>
-  <si>
-    <t>Metro Brands Ltd.</t>
-  </si>
-  <si>
-    <t>INE317I01021</t>
-  </si>
-  <si>
-    <t>The New India Assurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE470Y01017</t>
-  </si>
-  <si>
-    <t>Adani Wilmar Ltd</t>
-  </si>
-  <si>
-    <t>INE699H01024</t>
-  </si>
-  <si>
-    <t>Indian Overseas Bank</t>
-  </si>
-  <si>
-    <t>INE565A01014</t>
-  </si>
-  <si>
     <t>Mangalore Refinery and Petrochemicals Ltd.</t>
   </si>
   <si>
@@ -1120,6 +1129,9 @@
     <t>TREPS</t>
   </si>
   <si>
+    <t>^</t>
+  </si>
+  <si>
     <t>Net Current Assets</t>
   </si>
   <si>
@@ -1132,37 +1144,25 @@
     <t>Name of the Instrument</t>
   </si>
   <si>
-    <t>Jubilant Foodworks Limited</t>
-  </si>
-  <si>
-    <t>KEI Industries Ltd</t>
+    <t>FSN E-COMMERCE VENTURES LTD</t>
   </si>
   <si>
     <t>L&amp;T Finance Ltd (Old-L&amp;T Finance Holdings Ltd)</t>
   </si>
   <si>
-    <t>Mahindra &amp; Mahindra Financial Services Do Not Use</t>
-  </si>
-  <si>
-    <t>Oberoi Realty Ltd</t>
-  </si>
-  <si>
-    <t>Page Industries Limited</t>
-  </si>
-  <si>
-    <t>SBI Cards &amp; Payment Services Ltd</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
+    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
+  </si>
+  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -1172,9 +1172,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - Nifty Midcap 150 TRI</t>
   </si>
 </sst>
 </file>
@@ -1400,7 +1397,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1493,9 +1490,6 @@
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1592,13 +1586,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>212</xdr:row>
+      <xdr:row>208</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>222</xdr:row>
+      <xdr:row>218</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1616,8 +1610,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="40843200"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:off x="666750" y="40081200"/>
+          <a:ext cx="3686175" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1631,13 +1625,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>227</xdr:row>
+      <xdr:row>223</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>237</xdr:row>
+      <xdr:row>233</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1655,8 +1649,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="43700700"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:off x="666750" y="42938700"/>
+          <a:ext cx="3686175" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1989,19 +1983,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J226"/>
+  <dimension ref="B1:J221"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="27" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="27" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="27" width="16.571428571428573" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="27" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="27" width="50.285714285714285" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="27" width="10.857142857142858" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="27" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="27" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="27" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="27" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="26" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="26" width="55.285714285714285" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="26" width="16.857142857142858" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="26" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="26" width="50.285714285714285" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="26" width="10.857142857142858" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="26" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="26" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="26" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="26" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -2089,10 +2083,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>42264.26999999998</v>
+        <v>46532.790000000015</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9998586691954</v>
+        <v>0.9994125438438002</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -2126,10 +2120,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>42264.26999999998</v>
+        <v>46532.790000000015</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9998586691954</v>
+        <v>0.9994125438438002</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -2152,13 +2146,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>97622</v>
+        <v>54351</v>
       </c>
       <c r="G8" s="15">
-        <v>1036.01</v>
+        <v>1453.35</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0245092031609</v>
+        <v>0.0312144666289</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -2181,13 +2175,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>17830</v>
+        <v>1584209</v>
       </c>
       <c r="G9" s="15">
-        <v>946.05</v>
+        <v>1132.39</v>
       </c>
       <c r="H9" s="16">
-        <v>0.022380992124</v>
+        <v>0.0243210168685</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -2210,13 +2204,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>1556298</v>
+        <v>99194</v>
       </c>
       <c r="G10" s="15">
-        <v>905.30</v>
+        <v>1116.13</v>
       </c>
       <c r="H10" s="16">
-        <v>0.021416957</v>
+        <v>0.0239717911298</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -2239,13 +2233,13 @@
         <v>26</v>
       </c>
       <c r="F11" s="14">
-        <v>115643</v>
+        <v>14211</v>
       </c>
       <c r="G11" s="15">
-        <v>884.32</v>
+        <v>801.22</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0209206267693</v>
+        <v>0.0172082808356</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -2268,13 +2262,13 @@
         <v>29</v>
       </c>
       <c r="F12" s="14">
-        <v>13863</v>
+        <v>44167</v>
       </c>
       <c r="G12" s="15">
-        <v>836.30</v>
+        <v>778.05</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0197846030477</v>
+        <v>0.0167106448967</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -2294,16 +2288,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F13" s="14">
-        <v>5017</v>
+        <v>8890</v>
       </c>
       <c r="G13" s="15">
-        <v>751.85</v>
+        <v>760.14</v>
       </c>
       <c r="H13" s="16">
-        <v>0.017786743754</v>
+        <v>0.0163259811217</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -2314,25 +2308,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>35</v>
-      </c>
       <c r="F14" s="14">
-        <v>43441</v>
+        <v>5147</v>
       </c>
       <c r="G14" s="15">
-        <v>750.14</v>
+        <v>756.20</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0177462897647</v>
+        <v>0.0162413593868</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -2343,25 +2337,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="D15" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="F15" s="14">
-        <v>8753</v>
+        <v>176399</v>
       </c>
       <c r="G15" s="15">
-        <v>723.33</v>
+        <v>677.64</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0171120374537</v>
+        <v>0.0145540793108</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -2384,13 +2378,13 @@
         <v>40</v>
       </c>
       <c r="F16" s="14">
-        <v>31707</v>
+        <v>327232</v>
       </c>
       <c r="G16" s="15">
-        <v>659.65</v>
+        <v>661.20</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0156055403568</v>
+        <v>0.0142009876045</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -2410,16 +2404,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F17" s="14">
-        <v>321876</v>
+        <v>13541</v>
       </c>
       <c r="G17" s="15">
-        <v>602.58</v>
+        <v>647.67</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0142554180372</v>
+        <v>0.0139103957075</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -2430,25 +2424,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="D18" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>46</v>
-      </c>
       <c r="F18" s="14">
-        <v>163258</v>
+        <v>32238</v>
       </c>
       <c r="G18" s="15">
-        <v>566.83</v>
+        <v>631.12</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0134096694315</v>
+        <v>0.0135549414654</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -2459,25 +2453,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="F19" s="14">
-        <v>19070</v>
+        <v>18055</v>
       </c>
       <c r="G19" s="15">
-        <v>535.84</v>
+        <v>590.06</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0126765295912</v>
+        <v>0.0126730713035</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -2488,25 +2482,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>51</v>
-      </c>
       <c r="D20" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F20" s="14">
-        <v>84110</v>
+        <v>827475</v>
       </c>
       <c r="G20" s="15">
-        <v>533.97</v>
+        <v>562.43</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0126322904333</v>
+        <v>0.0120796452789</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -2517,25 +2511,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="D21" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="F21" s="14">
-        <v>17811</v>
+        <v>19367</v>
       </c>
       <c r="G21" s="15">
-        <v>519.02</v>
+        <v>554.09</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0122786137437</v>
+        <v>0.011900522114</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -2546,25 +2540,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>56</v>
-      </c>
       <c r="D22" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F22" s="14">
-        <v>13314</v>
+        <v>2516425</v>
       </c>
       <c r="G22" s="15">
-        <v>515.24</v>
+        <v>540.53</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0121891891358</v>
+        <v>0.0116092858891</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2575,25 +2569,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>43</v>
-      </c>
       <c r="F23" s="14">
-        <v>814099</v>
+        <v>128192</v>
       </c>
       <c r="G23" s="15">
-        <v>514.84</v>
+        <v>526.93</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0121797262144</v>
+        <v>0.0113171905602</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2613,16 +2607,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F24" s="14">
-        <v>17409</v>
+        <v>3251</v>
       </c>
       <c r="G24" s="15">
-        <v>491.20</v>
+        <v>523.54</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0116204675559</v>
+        <v>0.011244381504</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2633,25 +2627,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="D25" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F25" s="14">
-        <v>2476591</v>
+        <v>74916</v>
       </c>
       <c r="G25" s="15">
-        <v>476.25</v>
+        <v>519.21</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0112667908663</v>
+        <v>0.0111513835059</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2662,25 +2656,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="D26" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="F26" s="14">
-        <v>14020</v>
+        <v>34430</v>
       </c>
       <c r="G26" s="15">
-        <v>465.76</v>
+        <v>517.38</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0110186257509</v>
+        <v>0.0111120795021</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2691,25 +2685,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="D27" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>69</v>
-      </c>
       <c r="F27" s="14">
-        <v>69313</v>
+        <v>70432</v>
       </c>
       <c r="G27" s="15">
-        <v>464.85</v>
+        <v>504.61</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0109970976046</v>
+        <v>0.0108378105794</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2720,25 +2714,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>71</v>
-      </c>
       <c r="D28" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="F28" s="14">
-        <v>19818</v>
+        <v>69541</v>
       </c>
       <c r="G28" s="15">
-        <v>461.65</v>
+        <v>491.17</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0109213942329</v>
+        <v>0.0105491516662</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2749,25 +2743,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="F29" s="14">
-        <v>126187</v>
+        <v>9189</v>
       </c>
       <c r="G29" s="15">
-        <v>452.06</v>
+        <v>471.99</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0106945206908</v>
+        <v>0.0101372113422</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2778,25 +2772,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>43</v>
-      </c>
       <c r="F30" s="14">
-        <v>73696</v>
+        <v>20126</v>
       </c>
       <c r="G30" s="15">
-        <v>442.88</v>
+        <v>451.59</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0104773466433</v>
+        <v>0.0096990683489</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2807,25 +2801,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="D31" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F31" s="14">
-        <v>68449</v>
+        <v>190884</v>
       </c>
       <c r="G31" s="15">
-        <v>438.21</v>
+        <v>450.54</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0103668670352</v>
+        <v>0.0096765168713</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2845,16 +2839,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F32" s="14">
-        <v>36741</v>
+        <v>171526</v>
       </c>
       <c r="G32" s="15">
-        <v>430.57</v>
+        <v>445.68</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0101861252353</v>
+        <v>0.0095721357465</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2874,16 +2868,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="F33" s="14">
-        <v>14870</v>
+        <v>35587</v>
       </c>
       <c r="G33" s="15">
-        <v>426.46</v>
+        <v>441.60</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0100888937172</v>
+        <v>0.0094845071478</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2894,25 +2888,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="F34" s="14">
-        <v>34387</v>
+        <v>14351</v>
       </c>
       <c r="G34" s="15">
-        <v>420.91</v>
+        <v>439.44</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0099575956819</v>
+        <v>0.0094381155368</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2923,25 +2917,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F35" s="14">
-        <v>9041</v>
+        <v>24175</v>
       </c>
       <c r="G35" s="15">
-        <v>417.42</v>
+        <v>437.98</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0098750316922</v>
+        <v>0.0094067582441</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2964,13 +2958,13 @@
         <v>91</v>
       </c>
       <c r="F36" s="14">
-        <v>188172</v>
+        <v>17583</v>
       </c>
       <c r="G36" s="15">
-        <v>408.01</v>
+        <v>431.82</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0096524164648</v>
+        <v>0.0092744562422</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2990,16 +2984,16 @@
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F37" s="14">
-        <v>24496</v>
+        <v>37324</v>
       </c>
       <c r="G37" s="15">
-        <v>402.18</v>
+        <v>428.40</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0095144943844</v>
+        <v>0.0092010028581</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -3022,13 +3016,13 @@
         <v>96</v>
       </c>
       <c r="F38" s="14">
-        <v>66476</v>
+        <v>67540</v>
       </c>
       <c r="G38" s="15">
-        <v>401.35</v>
+        <v>424.08</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0094948588224</v>
+        <v>0.009108219636</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -3048,16 +3042,16 @@
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="F39" s="14">
-        <v>6608</v>
+        <v>10814</v>
       </c>
       <c r="G39" s="15">
-        <v>398.99</v>
+        <v>413.49</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0094390275858</v>
+        <v>0.0088807718762</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -3077,16 +3071,16 @@
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F40" s="14">
-        <v>30005</v>
+        <v>45429</v>
       </c>
       <c r="G40" s="15">
-        <v>378.32</v>
+        <v>404.52</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0089500311192</v>
+        <v>0.0086881178248</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -3106,16 +3100,16 @@
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="F41" s="14">
-        <v>33889</v>
+        <v>6730</v>
       </c>
       <c r="G41" s="15">
-        <v>378.12</v>
+        <v>403.19</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0089452996585</v>
+        <v>0.0086595526198</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -3126,25 +3120,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="D42" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>96</v>
-      </c>
       <c r="F42" s="14">
-        <v>10666</v>
+        <v>478602</v>
       </c>
       <c r="G42" s="15">
-        <v>371.58</v>
+        <v>402.41</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0087905808926</v>
+        <v>0.0086428000936</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -3167,13 +3161,13 @@
         <v>108</v>
       </c>
       <c r="F43" s="14">
-        <v>818</v>
+        <v>840</v>
       </c>
       <c r="G43" s="15">
-        <v>365.84</v>
+        <v>389.59</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0086547879696</v>
+        <v>0.008367457291</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -3193,16 +3187,16 @@
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="F44" s="14">
-        <v>24990</v>
+        <v>15174</v>
       </c>
       <c r="G44" s="15">
-        <v>365.72</v>
+        <v>388.27</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0086519490931</v>
+        <v>0.008339106862</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -3213,25 +3207,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>113</v>
-      </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="F45" s="14">
-        <v>23786</v>
+        <v>30379</v>
       </c>
       <c r="G45" s="15">
-        <v>359.06</v>
+        <v>383.63</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0084943914508</v>
+        <v>0.0082394508087</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -3242,25 +3236,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C46" s="13" t="s">
-        <v>115</v>
-      </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="F46" s="14">
-        <v>74586</v>
+        <v>24884</v>
       </c>
       <c r="G46" s="15">
-        <v>355.25</v>
+        <v>382.49</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0084042571239</v>
+        <v>0.0082149663473</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -3271,10 +3265,10 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
@@ -3283,13 +3277,13 @@
         <v>40</v>
       </c>
       <c r="F47" s="14">
-        <v>6981</v>
+        <v>257857</v>
       </c>
       <c r="G47" s="15">
-        <v>353.45</v>
+        <v>378.51</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0083616739773</v>
+        <v>0.0081294855084</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -3300,25 +3294,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="F48" s="14">
-        <v>50147</v>
+        <v>270</v>
       </c>
       <c r="G48" s="15">
-        <v>352.98</v>
+        <v>374.94</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0083505550446</v>
+        <v>0.0080528104846</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -3329,25 +3323,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F49" s="14">
-        <v>44633</v>
+        <v>15067</v>
       </c>
       <c r="G49" s="15">
-        <v>346.24</v>
+        <v>371.81</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0081911048179</v>
+        <v>0.0079855856038</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -3358,25 +3352,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="F50" s="14">
-        <v>471079</v>
+        <v>16514</v>
       </c>
       <c r="G50" s="15">
-        <v>342.33</v>
+        <v>370.14</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0080986047606</v>
+        <v>0.0079497180156</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -3387,25 +3381,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="F51" s="14">
-        <v>8490</v>
+        <v>181869</v>
       </c>
       <c r="G51" s="15">
-        <v>336.95</v>
+        <v>369.67</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0079713284669</v>
+        <v>0.0079396235447</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -3416,25 +3410,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>40</v>
-      </c>
       <c r="F52" s="14">
-        <v>13655</v>
+        <v>422229</v>
       </c>
       <c r="G52" s="15">
-        <v>332.55</v>
+        <v>369.07</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0078672363309</v>
+        <v>0.007926736986</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -3445,25 +3439,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C53" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C53" s="13" t="s">
-        <v>131</v>
-      </c>
       <c r="D53" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F53" s="14">
-        <v>3199</v>
+        <v>39972</v>
       </c>
       <c r="G53" s="15">
-        <v>326.13</v>
+        <v>368.16</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0077153564414</v>
+        <v>0.0079071923721</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -3474,25 +3468,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C54" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>133</v>
-      </c>
       <c r="D54" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F54" s="14">
-        <v>8096</v>
+        <v>7095</v>
       </c>
       <c r="G54" s="15">
-        <v>325.75</v>
+        <v>361.74</v>
       </c>
       <c r="H54" s="16">
-        <v>0.007706366666</v>
+        <v>0.0077693061948</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -3503,25 +3497,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C55" s="13" t="s">
-        <v>135</v>
-      </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F55" s="14">
-        <v>14083</v>
+        <v>15757</v>
       </c>
       <c r="G55" s="15">
-        <v>318.11</v>
+        <v>360.74</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0075256248661</v>
+        <v>0.0077478285971</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -3532,25 +3526,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C56" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C56" s="13" t="s">
-        <v>137</v>
-      </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="F56" s="14">
-        <v>98466</v>
+        <v>8627</v>
       </c>
       <c r="G56" s="15">
-        <v>311.35</v>
+        <v>357.69</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0073657014933</v>
+        <v>0.0076823219241</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -3561,25 +3555,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="F57" s="14">
-        <v>3410251</v>
+        <v>25389</v>
       </c>
       <c r="G57" s="15">
-        <v>308.63</v>
+        <v>348.84</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0073013536274</v>
+        <v>0.0074922451844</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3590,25 +3584,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C58" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>88</v>
-      </c>
       <c r="F58" s="14">
-        <v>39337</v>
+        <v>50784</v>
       </c>
       <c r="G58" s="15">
-        <v>306.12</v>
+        <v>332.91</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0072419737952</v>
+        <v>0.0071501070529</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3619,25 +3613,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C59" s="13" t="s">
-        <v>144</v>
-      </c>
       <c r="D59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F59" s="14">
-        <v>266</v>
+        <v>22512</v>
       </c>
       <c r="G59" s="15">
-        <v>302.26</v>
+        <v>330.16</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0071506566031</v>
+        <v>0.0070910436592</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3648,25 +3642,25 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="D60" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D60" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>147</v>
-      </c>
       <c r="F60" s="14">
-        <v>178930</v>
+        <v>461235</v>
       </c>
       <c r="G60" s="15">
-        <v>302.21</v>
+        <v>328.26</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0071494737379</v>
+        <v>0.0070502362236</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3677,25 +3671,25 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C61" s="13" t="s">
-        <v>149</v>
-      </c>
       <c r="D61" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F61" s="14">
-        <v>21421</v>
+        <v>1694</v>
       </c>
       <c r="G61" s="15">
-        <v>301.86</v>
+        <v>326.91</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0071411936816</v>
+        <v>0.0070212414667</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3706,25 +3700,25 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C62" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C62" s="13" t="s">
-        <v>151</v>
-      </c>
       <c r="D62" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F62" s="14">
-        <v>22159</v>
+        <v>59872</v>
       </c>
       <c r="G62" s="15">
-        <v>301.25</v>
+        <v>325.67</v>
       </c>
       <c r="H62" s="16">
-        <v>0.0071267627264</v>
+        <v>0.0069946092455</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3735,25 +3729,25 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C63" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C63" s="13" t="s">
-        <v>153</v>
-      </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="F63" s="14">
-        <v>71640</v>
+        <v>14316</v>
       </c>
       <c r="G63" s="15">
-        <v>301.21</v>
+        <v>317.16</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0071258164343</v>
+        <v>0.006811834889</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3764,25 +3758,25 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C64" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>157</v>
-      </c>
       <c r="F64" s="14">
-        <v>453988</v>
+        <v>72783</v>
       </c>
       <c r="G64" s="15">
-        <v>300.09</v>
+        <v>310.64</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0070993202542</v>
+        <v>0.006671800952</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3793,25 +3787,25 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C65" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="F65" s="14">
-        <v>58859</v>
+        <v>100020</v>
       </c>
       <c r="G65" s="15">
-        <v>296.83</v>
+        <v>307.36</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0070221974443</v>
+        <v>0.0066013544315</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3822,25 +3816,25 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C66" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="D66" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="D66" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="F66" s="14">
-        <v>10557</v>
+        <v>75751</v>
       </c>
       <c r="G66" s="15">
-        <v>292.56</v>
+        <v>307.21</v>
       </c>
       <c r="H66" s="16">
-        <v>0.0069211807576</v>
+        <v>0.0065981327918</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3860,16 +3854,16 @@
         <v>13</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="F67" s="14">
-        <v>4553</v>
+        <v>5586</v>
       </c>
       <c r="G67" s="15">
-        <v>288.48</v>
+        <v>307.09</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0068246589587</v>
+        <v>0.0065955554801</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3880,25 +3874,25 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>29</v>
+        <v>141</v>
       </c>
       <c r="F68" s="14">
-        <v>3101</v>
+        <v>40256</v>
       </c>
       <c r="G68" s="15">
-        <v>282.87</v>
+        <v>304.34</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0066919414852</v>
+        <v>0.0065364920864</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3909,25 +3903,25 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c r="F69" s="14">
-        <v>36209</v>
+        <v>4626</v>
       </c>
       <c r="G69" s="15">
-        <v>282.47</v>
+        <v>297.89</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0066824785638</v>
+        <v>0.0063979615812</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3947,16 +3941,16 @@
         <v>13</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F70" s="14">
-        <v>15461</v>
+        <v>8230</v>
       </c>
       <c r="G70" s="15">
-        <v>280.25</v>
+        <v>297.12</v>
       </c>
       <c r="H70" s="16">
-        <v>0.0066299593496</v>
+        <v>0.006381423831</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3976,16 +3970,16 @@
         <v>13</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="F71" s="14">
-        <v>42858</v>
+        <v>20107</v>
       </c>
       <c r="G71" s="15">
-        <v>279.99</v>
+        <v>292.98</v>
       </c>
       <c r="H71" s="16">
-        <v>0.0066238084507</v>
+        <v>0.0062925065764</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>13</v>
@@ -3996,25 +3990,25 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C72" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="C72" s="13" t="s">
-        <v>175</v>
-      </c>
       <c r="D72" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="F72" s="14">
-        <v>15451</v>
+        <v>21784</v>
       </c>
       <c r="G72" s="15">
-        <v>279.59</v>
+        <v>291.43</v>
       </c>
       <c r="H72" s="16">
-        <v>0.0066143455292</v>
+        <v>0.0062592163</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>13</v>
@@ -4025,25 +4019,25 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C73" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="C73" s="13" t="s">
-        <v>177</v>
-      </c>
       <c r="D73" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>178</v>
+        <v>40</v>
       </c>
       <c r="F73" s="14">
-        <v>5497</v>
+        <v>47188</v>
       </c>
       <c r="G73" s="15">
-        <v>265.77</v>
+        <v>290.96</v>
       </c>
       <c r="H73" s="16">
-        <v>0.0062874015927</v>
+        <v>0.0062491218291</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>13</v>
@@ -4054,25 +4048,25 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="C74" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="13" t="s">
-        <v>69</v>
-      </c>
       <c r="F74" s="14">
-        <v>14416</v>
+        <v>36813</v>
       </c>
       <c r="G74" s="15">
-        <v>263.03</v>
+        <v>288.76</v>
       </c>
       <c r="H74" s="16">
-        <v>0.0062225805807</v>
+        <v>0.0062018711141</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>13</v>
@@ -4083,25 +4077,25 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C75" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="C75" s="13" t="s">
-        <v>182</v>
-      </c>
       <c r="D75" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F75" s="14">
-        <v>46417</v>
+        <v>51286</v>
       </c>
       <c r="G75" s="15">
-        <v>257.96</v>
+        <v>287.41</v>
       </c>
       <c r="H75" s="16">
-        <v>0.0061026380511</v>
+        <v>0.0061728763572</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>13</v>
@@ -4112,25 +4106,25 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C76" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="D76" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="D76" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>40</v>
-      </c>
       <c r="F76" s="14">
-        <v>17840</v>
+        <v>8193</v>
       </c>
       <c r="G76" s="15">
-        <v>257.48</v>
+        <v>284.97</v>
       </c>
       <c r="H76" s="16">
-        <v>0.0060912825454</v>
+        <v>0.0061204710188</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>13</v>
@@ -4150,16 +4144,16 @@
         <v>13</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="F77" s="14">
-        <v>50378</v>
+        <v>43282</v>
       </c>
       <c r="G77" s="15">
-        <v>253.45</v>
+        <v>279.06</v>
       </c>
       <c r="H77" s="16">
-        <v>0.0059959436116</v>
+        <v>0.0059935384164</v>
       </c>
       <c r="I77" s="15" t="s">
         <v>13</v>
@@ -4170,25 +4164,25 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="F78" s="14">
-        <v>15426</v>
+        <v>15718</v>
       </c>
       <c r="G78" s="15">
-        <v>251.91</v>
+        <v>274.48</v>
       </c>
       <c r="H78" s="16">
-        <v>0.005959511364</v>
+        <v>0.0058951710188</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>13</v>
@@ -4199,25 +4193,25 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="F79" s="14">
-        <v>16238</v>
+        <v>3158</v>
       </c>
       <c r="G79" s="15">
-        <v>244.76</v>
+        <v>267.25</v>
       </c>
       <c r="H79" s="16">
-        <v>0.0057903616429</v>
+        <v>0.0057398879874</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>13</v>
@@ -4228,25 +4222,25 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="F80" s="14">
-        <v>39505</v>
+        <v>17317</v>
       </c>
       <c r="G80" s="15">
-        <v>236.28</v>
+        <v>265.35</v>
       </c>
       <c r="H80" s="16">
-        <v>0.0055897477079</v>
+        <v>0.0056990805518</v>
       </c>
       <c r="I80" s="15" t="s">
         <v>13</v>
@@ -4257,25 +4251,25 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
       <c r="B81" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F81" s="14">
-        <v>59783</v>
+        <v>18559</v>
       </c>
       <c r="G81" s="15">
-        <v>223.89</v>
+        <v>264.43</v>
       </c>
       <c r="H81" s="16">
-        <v>0.0052966337156</v>
+        <v>0.0056793211619</v>
       </c>
       <c r="I81" s="15" t="s">
         <v>13</v>
@@ -4286,25 +4280,25 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F82" s="14">
-        <v>23485</v>
+        <v>10694</v>
       </c>
       <c r="G82" s="15">
-        <v>222.07</v>
+        <v>264.38</v>
       </c>
       <c r="H82" s="16">
-        <v>0.0052535774229</v>
+        <v>0.005678247282</v>
       </c>
       <c r="I82" s="15" t="s">
         <v>13</v>
@@ -4315,25 +4309,25 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
       <c r="B83" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="F83" s="14">
-        <v>77727</v>
+        <v>15684</v>
       </c>
       <c r="G83" s="15">
-        <v>221.48</v>
+        <v>262.9</v>
       </c>
       <c r="H83" s="16">
-        <v>0.0052396196138</v>
+        <v>0.0056464604374</v>
       </c>
       <c r="I83" s="15" t="s">
         <v>13</v>
@@ -4344,25 +4338,25 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="F84" s="14">
-        <v>66956</v>
+        <v>3686770</v>
       </c>
       <c r="G84" s="15">
-        <v>214.96</v>
+        <v>255.12</v>
       </c>
       <c r="H84" s="16">
-        <v>0.0050853739939</v>
+        <v>0.0054793647272</v>
       </c>
       <c r="I84" s="15" t="s">
         <v>13</v>
@@ -4373,25 +4367,25 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>40</v>
+        <v>158</v>
       </c>
       <c r="F85" s="14">
-        <v>59133</v>
+        <v>37043</v>
       </c>
       <c r="G85" s="15">
-        <v>214.39</v>
+        <v>253.28</v>
       </c>
       <c r="H85" s="16">
-        <v>0.0050718893308</v>
+        <v>0.0054398459474</v>
       </c>
       <c r="I85" s="15" t="s">
         <v>13</v>
@@ -4402,25 +4396,25 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="F86" s="14">
-        <v>9889</v>
+        <v>193039</v>
       </c>
       <c r="G86" s="15">
-        <v>212.22</v>
+        <v>249.37</v>
       </c>
       <c r="H86" s="16">
-        <v>0.0050205529819</v>
+        <v>0.0053558685404</v>
       </c>
       <c r="I86" s="15" t="s">
         <v>13</v>
@@ -4440,16 +4434,16 @@
         <v>13</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>49</v>
+        <v>208</v>
       </c>
       <c r="F87" s="14">
-        <v>9027</v>
+        <v>12309</v>
       </c>
       <c r="G87" s="15">
-        <v>209.93</v>
+        <v>248.09</v>
       </c>
       <c r="H87" s="16">
-        <v>0.0049663777565</v>
+        <v>0.0053283772153</v>
       </c>
       <c r="I87" s="15" t="s">
         <v>13</v>
@@ -4460,25 +4454,25 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>173</v>
+        <v>68</v>
       </c>
       <c r="F88" s="14">
-        <v>189886</v>
+        <v>14800</v>
       </c>
       <c r="G88" s="15">
-        <v>203.99</v>
+        <v>247.35</v>
       </c>
       <c r="H88" s="16">
-        <v>0.0048258533728</v>
+        <v>0.005312483793</v>
       </c>
       <c r="I88" s="15" t="s">
         <v>13</v>
@@ -4489,25 +4483,25 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F89" s="14">
-        <v>20573</v>
+        <v>16454</v>
       </c>
       <c r="G89" s="15">
-        <v>202.87</v>
+        <v>246.50</v>
       </c>
       <c r="H89" s="16">
-        <v>0.0047993571927</v>
+        <v>0.005294227835</v>
       </c>
       <c r="I89" s="15" t="s">
         <v>13</v>
@@ -4518,25 +4512,25 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="F90" s="14">
-        <v>8060</v>
+        <v>23874</v>
       </c>
       <c r="G90" s="15">
-        <v>201.38</v>
+        <v>240.33</v>
       </c>
       <c r="H90" s="16">
-        <v>0.0047641078103</v>
+        <v>0.0051617110571</v>
       </c>
       <c r="I90" s="15" t="s">
         <v>13</v>
@@ -4556,16 +4550,16 @@
         <v>13</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="F91" s="14">
-        <v>15945</v>
+        <v>40153</v>
       </c>
       <c r="G91" s="15">
-        <v>197.57</v>
+        <v>239.49</v>
       </c>
       <c r="H91" s="16">
-        <v>0.0046739734833</v>
+        <v>0.005143669875</v>
       </c>
       <c r="I91" s="15" t="s">
         <v>13</v>
@@ -4585,16 +4579,16 @@
         <v>13</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="F92" s="14">
-        <v>5087</v>
+        <v>60772</v>
       </c>
       <c r="G92" s="15">
-        <v>196.54</v>
+        <v>235.10</v>
       </c>
       <c r="H92" s="16">
-        <v>0.0046496064606</v>
+        <v>0.0050493832211</v>
       </c>
       <c r="I92" s="15" t="s">
         <v>13</v>
@@ -4614,16 +4608,16 @@
         <v>13</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>221</v>
+        <v>73</v>
       </c>
       <c r="F93" s="14">
-        <v>3606</v>
+        <v>88871</v>
       </c>
       <c r="G93" s="15">
-        <v>196.50</v>
+        <v>232.04</v>
       </c>
       <c r="H93" s="16">
-        <v>0.0046486601684</v>
+        <v>0.0049836617721</v>
       </c>
       <c r="I93" s="15" t="s">
         <v>13</v>
@@ -4634,25 +4628,25 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C94" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="C94" s="13" t="s">
-        <v>223</v>
-      </c>
       <c r="D94" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="F94" s="14">
-        <v>10500</v>
+        <v>16234</v>
       </c>
       <c r="G94" s="15">
-        <v>195.97</v>
+        <v>226.16</v>
       </c>
       <c r="H94" s="16">
-        <v>0.0046361217975</v>
+        <v>0.0048573734976</v>
       </c>
       <c r="I94" s="15" t="s">
         <v>13</v>
@@ -4663,25 +4657,25 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
       <c r="B95" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C95" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C95" s="13" t="s">
-        <v>225</v>
-      </c>
       <c r="D95" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="F95" s="14">
-        <v>5365</v>
+        <v>5370</v>
       </c>
       <c r="G95" s="15">
-        <v>191.94</v>
+        <v>224.93</v>
       </c>
       <c r="H95" s="16">
-        <v>0.0045407828637</v>
+        <v>0.0048309560524</v>
       </c>
       <c r="I95" s="15" t="s">
         <v>13</v>
@@ -4692,25 +4686,25 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C96" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="D96" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="D96" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E96" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="F96" s="14">
-        <v>43720</v>
+        <v>48965</v>
       </c>
       <c r="G96" s="15">
-        <v>191.19</v>
+        <v>224.36</v>
       </c>
       <c r="H96" s="16">
-        <v>0.004523039886</v>
+        <v>0.0048187138217</v>
       </c>
       <c r="I96" s="15" t="s">
         <v>13</v>
@@ -4730,16 +4724,16 @@
         <v>13</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>54</v>
+        <v>184</v>
       </c>
       <c r="F97" s="14">
-        <v>5099</v>
+        <v>11300</v>
       </c>
       <c r="G97" s="15">
-        <v>187.67</v>
+        <v>220.02</v>
       </c>
       <c r="H97" s="16">
-        <v>0.0044397661771</v>
+        <v>0.0047255010477</v>
       </c>
       <c r="I97" s="15" t="s">
         <v>13</v>
@@ -4759,16 +4753,16 @@
         <v>13</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="F98" s="14">
-        <v>92141</v>
+        <v>38024</v>
       </c>
       <c r="G98" s="15">
-        <v>185.94</v>
+        <v>216.09</v>
       </c>
       <c r="H98" s="16">
-        <v>0.0043988390418</v>
+        <v>0.0046410940887</v>
       </c>
       <c r="I98" s="15" t="s">
         <v>13</v>
@@ -4788,16 +4782,16 @@
         <v>13</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>66</v>
+        <v>227</v>
       </c>
       <c r="F99" s="14">
-        <v>5290</v>
+        <v>119751</v>
       </c>
       <c r="G99" s="15">
-        <v>181.22</v>
+        <v>215.97</v>
       </c>
       <c r="H99" s="16">
-        <v>0.0042871765685</v>
+        <v>0.004638516777</v>
       </c>
       <c r="I99" s="15" t="s">
         <v>13</v>
@@ -4817,16 +4811,16 @@
         <v>13</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>61</v>
+        <v>164</v>
       </c>
       <c r="F100" s="14">
-        <v>1243</v>
+        <v>10633</v>
       </c>
       <c r="G100" s="15">
-        <v>180.24</v>
+        <v>214.40</v>
       </c>
       <c r="H100" s="16">
-        <v>0.004263992411</v>
+        <v>0.0046047969485</v>
       </c>
       <c r="I100" s="15" t="s">
         <v>13</v>
@@ -4846,16 +4840,16 @@
         <v>13</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F101" s="14">
-        <v>159614</v>
+        <v>21416</v>
       </c>
       <c r="G101" s="15">
-        <v>179.60</v>
+        <v>213.61</v>
       </c>
       <c r="H101" s="16">
-        <v>0.0042488517366</v>
+        <v>0.0045878296464</v>
       </c>
       <c r="I101" s="15" t="s">
         <v>13</v>
@@ -4875,16 +4869,16 @@
         <v>13</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="F102" s="14">
-        <v>8937</v>
+        <v>95229</v>
       </c>
       <c r="G102" s="15">
-        <v>179.42</v>
+        <v>211.89</v>
       </c>
       <c r="H102" s="16">
-        <v>0.004244593422</v>
+        <v>0.0045508881783</v>
       </c>
       <c r="I102" s="15" t="s">
         <v>13</v>
@@ -4904,16 +4898,16 @@
         <v>13</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F103" s="14">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="G103" s="15">
-        <v>179.03</v>
+        <v>211.66</v>
       </c>
       <c r="H103" s="16">
-        <v>0.0042353670735</v>
+        <v>0.0045459483308</v>
       </c>
       <c r="I103" s="15" t="s">
         <v>13</v>
@@ -4933,16 +4927,16 @@
         <v>13</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="F104" s="14">
-        <v>88500</v>
+        <v>2807</v>
       </c>
       <c r="G104" s="15">
-        <v>178.87</v>
+        <v>210.68</v>
       </c>
       <c r="H104" s="16">
-        <v>0.004231581905</v>
+        <v>0.0045249002851</v>
       </c>
       <c r="I104" s="15" t="s">
         <v>13</v>
@@ -4962,16 +4956,16 @@
         <v>13</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="F105" s="14">
-        <v>1381</v>
+        <v>43070</v>
       </c>
       <c r="G105" s="15">
-        <v>177.65</v>
+        <v>202.67</v>
       </c>
       <c r="H105" s="16">
-        <v>0.0042027199945</v>
+        <v>0.0043528647274</v>
       </c>
       <c r="I105" s="15" t="s">
         <v>13</v>
@@ -4991,16 +4985,16 @@
         <v>13</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F106" s="14">
-        <v>23752</v>
+        <v>60142</v>
       </c>
       <c r="G106" s="15">
-        <v>177.34</v>
+        <v>201.99</v>
       </c>
       <c r="H106" s="16">
-        <v>0.0041953862304</v>
+        <v>0.004338259961</v>
       </c>
       <c r="I106" s="15" t="s">
         <v>13</v>
@@ -5020,16 +5014,16 @@
         <v>13</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F107" s="14">
-        <v>37406</v>
+        <v>162265</v>
       </c>
       <c r="G107" s="15">
-        <v>176.84</v>
+        <v>197.87</v>
       </c>
       <c r="H107" s="16">
-        <v>0.0041835575785</v>
+        <v>0.0042497722584</v>
       </c>
       <c r="I107" s="15" t="s">
         <v>13</v>
@@ -5049,16 +5043,16 @@
         <v>13</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>252</v>
+        <v>53</v>
       </c>
       <c r="F108" s="14">
-        <v>39168</v>
+        <v>5450</v>
       </c>
       <c r="G108" s="15">
-        <v>176.31</v>
+        <v>193.65</v>
       </c>
       <c r="H108" s="16">
-        <v>0.0041710192076</v>
+        <v>0.0041591367961</v>
       </c>
       <c r="I108" s="15" t="s">
         <v>13</v>
@@ -5069,25 +5063,25 @@
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
       <c r="B109" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="C109" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C109" s="13" t="s">
-        <v>254</v>
-      </c>
       <c r="D109" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="F109" s="14">
-        <v>3201</v>
+        <v>93667</v>
       </c>
       <c r="G109" s="15">
-        <v>173.92</v>
+        <v>193.57</v>
       </c>
       <c r="H109" s="16">
-        <v>0.0041144782519</v>
+        <v>0.0041574185883</v>
       </c>
       <c r="I109" s="15" t="s">
         <v>13</v>
@@ -5098,25 +5092,25 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
       <c r="B110" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="C110" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="C110" s="13" t="s">
+      <c r="D110" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="D110" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="F110" s="14">
-        <v>14643</v>
+        <v>9637</v>
       </c>
       <c r="G110" s="15">
-        <v>173.77</v>
+        <v>190.50</v>
       </c>
       <c r="H110" s="16">
-        <v>0.0041109296563</v>
+        <v>0.0040914823633</v>
       </c>
       <c r="I110" s="15" t="s">
         <v>13</v>
@@ -5136,16 +5130,16 @@
         <v>13</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F111" s="14">
-        <v>2762</v>
+        <v>110933</v>
       </c>
       <c r="G111" s="15">
-        <v>173.12</v>
+        <v>188.80</v>
       </c>
       <c r="H111" s="16">
-        <v>0.0040955524089</v>
+        <v>0.0040549704472</v>
       </c>
       <c r="I111" s="15" t="s">
         <v>13</v>
@@ -5165,16 +5159,16 @@
         <v>13</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>214</v>
+        <v>53</v>
       </c>
       <c r="F112" s="14">
-        <v>11118</v>
+        <v>9176</v>
       </c>
       <c r="G112" s="15">
-        <v>170.36</v>
+        <v>186.03</v>
       </c>
       <c r="H112" s="16">
-        <v>0.0040302582508</v>
+        <v>0.0039954775016</v>
       </c>
       <c r="I112" s="15" t="s">
         <v>13</v>
@@ -5194,16 +5188,16 @@
         <v>13</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="F113" s="14">
-        <v>93501</v>
+        <v>10041</v>
       </c>
       <c r="G113" s="15">
-        <v>167.73</v>
+        <v>183.82</v>
       </c>
       <c r="H113" s="16">
-        <v>0.0039680395422</v>
+        <v>0.0039480120106</v>
       </c>
       <c r="I113" s="15" t="s">
         <v>13</v>
@@ -5223,16 +5217,16 @@
         <v>13</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="F114" s="14">
-        <v>40616</v>
+        <v>107167</v>
       </c>
       <c r="G114" s="15">
-        <v>167.11</v>
+        <v>183.57</v>
       </c>
       <c r="H114" s="16">
-        <v>0.003953372014</v>
+        <v>0.0039426426112</v>
       </c>
       <c r="I114" s="15" t="s">
         <v>13</v>
@@ -5252,16 +5246,16 @@
         <v>13</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F115" s="14">
-        <v>109271</v>
+        <v>2253</v>
       </c>
       <c r="G115" s="15">
-        <v>165.41</v>
+        <v>182.81</v>
       </c>
       <c r="H115" s="16">
-        <v>0.0039131545977</v>
+        <v>0.003926319637</v>
       </c>
       <c r="I115" s="15" t="s">
         <v>13</v>
@@ -5281,16 +5275,16 @@
         <v>13</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>221</v>
+        <v>45</v>
       </c>
       <c r="F116" s="14">
-        <v>20256</v>
+        <v>5527</v>
       </c>
       <c r="G116" s="15">
-        <v>159.54</v>
+        <v>182.31</v>
       </c>
       <c r="H116" s="16">
-        <v>0.0037742862253</v>
+        <v>0.0039155808381</v>
       </c>
       <c r="I116" s="15" t="s">
         <v>13</v>
@@ -5310,16 +5304,16 @@
         <v>13</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F117" s="14">
-        <v>10453</v>
+        <v>5182</v>
       </c>
       <c r="G117" s="15">
-        <v>159.38</v>
+        <v>181.26</v>
       </c>
       <c r="H117" s="16">
-        <v>0.0037705010567</v>
+        <v>0.0038930293605</v>
       </c>
       <c r="I117" s="15" t="s">
         <v>13</v>
@@ -5339,16 +5333,16 @@
         <v>13</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="F118" s="14">
-        <v>4361</v>
+        <v>5171</v>
       </c>
       <c r="G118" s="15">
-        <v>158.02</v>
+        <v>175.20</v>
       </c>
       <c r="H118" s="16">
-        <v>0.0037383271237</v>
+        <v>0.0037628751184</v>
       </c>
       <c r="I118" s="15" t="s">
         <v>13</v>
@@ -5368,16 +5362,16 @@
         <v>13</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>275</v>
+        <v>17</v>
       </c>
       <c r="F119" s="14">
-        <v>12105</v>
+        <v>23359</v>
       </c>
       <c r="G119" s="15">
-        <v>157.97</v>
+        <v>173.08</v>
       </c>
       <c r="H119" s="16">
-        <v>0.0037371442585</v>
+        <v>0.0037173426113</v>
       </c>
       <c r="I119" s="15" t="s">
         <v>13</v>
@@ -5388,25 +5382,25 @@
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1">
       <c r="B120" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C120" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="C120" s="13" t="s">
-        <v>277</v>
-      </c>
       <c r="D120" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="F120" s="14">
-        <v>105742</v>
+        <v>3253</v>
       </c>
       <c r="G120" s="15">
-        <v>153.82</v>
+        <v>170.77</v>
       </c>
       <c r="H120" s="16">
-        <v>0.0036389664484</v>
+        <v>0.0036677293605</v>
       </c>
       <c r="I120" s="15" t="s">
         <v>13</v>
@@ -5417,25 +5411,25 @@
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1">
       <c r="B121" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="C121" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="C121" s="13" t="s">
-        <v>279</v>
-      </c>
       <c r="D121" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="F121" s="14">
-        <v>55972</v>
+        <v>41291</v>
       </c>
       <c r="G121" s="15">
-        <v>153.28</v>
+        <v>169.95</v>
       </c>
       <c r="H121" s="16">
-        <v>0.0036261915044</v>
+        <v>0.0036501177304</v>
       </c>
       <c r="I121" s="15" t="s">
         <v>13</v>
@@ -5446,25 +5440,25 @@
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1">
       <c r="B122" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C122" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="C122" s="13" t="s">
-        <v>281</v>
-      </c>
       <c r="D122" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>61</v>
+        <v>164</v>
       </c>
       <c r="F122" s="14">
-        <v>25902</v>
+        <v>9001</v>
       </c>
       <c r="G122" s="15">
-        <v>152.73</v>
+        <v>169.47</v>
       </c>
       <c r="H122" s="16">
-        <v>0.0036131799874</v>
+        <v>0.0036398084835</v>
       </c>
       <c r="I122" s="15" t="s">
         <v>13</v>
@@ -5475,25 +5469,25 @@
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1">
       <c r="B123" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C123" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="C123" s="13" t="s">
-        <v>283</v>
-      </c>
       <c r="D123" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F123" s="14">
-        <v>14528</v>
+        <v>10625</v>
       </c>
       <c r="G123" s="15">
-        <v>151.7</v>
+        <v>168.79</v>
       </c>
       <c r="H123" s="16">
-        <v>0.0035888129646</v>
+        <v>0.0036252037171</v>
       </c>
       <c r="I123" s="15" t="s">
         <v>13</v>
@@ -5504,25 +5498,25 @@
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1">
       <c r="B124" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C124" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="C124" s="13" t="s">
-        <v>285</v>
-      </c>
       <c r="D124" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="F124" s="14">
-        <v>65920</v>
+        <v>25249</v>
       </c>
       <c r="G124" s="15">
-        <v>151.42</v>
+        <v>163.25</v>
       </c>
       <c r="H124" s="16">
-        <v>0.0035821889196</v>
+        <v>0.0035062178258</v>
       </c>
       <c r="I124" s="15" t="s">
         <v>13</v>
@@ -5533,25 +5527,25 @@
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1">
       <c r="B125" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="C125" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="C125" s="13" t="s">
-        <v>287</v>
-      </c>
       <c r="D125" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="F125" s="14">
-        <v>260631</v>
+        <v>67014</v>
       </c>
       <c r="G125" s="15">
-        <v>149.39</v>
+        <v>161.66</v>
       </c>
       <c r="H125" s="16">
-        <v>0.0035341645932</v>
+        <v>0.0034720684454</v>
       </c>
       <c r="I125" s="15" t="s">
         <v>13</v>
@@ -5562,25 +5556,25 @@
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1">
       <c r="B126" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C126" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="C126" s="13" t="s">
-        <v>289</v>
-      </c>
       <c r="D126" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F126" s="14">
-        <v>5530</v>
+        <v>19840</v>
       </c>
       <c r="G126" s="15">
-        <v>149</v>
+        <v>160.68</v>
       </c>
       <c r="H126" s="16">
-        <v>0.0035249382447</v>
+        <v>0.0034510203997</v>
       </c>
       <c r="I126" s="15" t="s">
         <v>13</v>
@@ -5591,25 +5585,25 @@
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1">
       <c r="B127" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="C127" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="C127" s="13" t="s">
+      <c r="D127" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="D127" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="F127" s="14">
-        <v>4718</v>
+        <v>3665</v>
       </c>
       <c r="G127" s="15">
-        <v>134.83</v>
+        <v>160.07</v>
       </c>
       <c r="H127" s="16">
-        <v>0.0031897142519</v>
+        <v>0.0034379190651</v>
       </c>
       <c r="I127" s="15" t="s">
         <v>13</v>
@@ -5629,16 +5623,16 @@
         <v>13</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>46</v>
+        <v>291</v>
       </c>
       <c r="F128" s="14">
-        <v>9879</v>
+        <v>20594</v>
       </c>
       <c r="G128" s="15">
-        <v>133.85</v>
+        <v>159.32</v>
       </c>
       <c r="H128" s="16">
-        <v>0.0031665300943</v>
+        <v>0.0034218108668</v>
       </c>
       <c r="I128" s="15" t="s">
         <v>13</v>
@@ -5658,16 +5652,16 @@
         <v>13</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="F129" s="14">
-        <v>22883</v>
+        <v>89971</v>
       </c>
       <c r="G129" s="15">
-        <v>133.59</v>
+        <v>157.21</v>
       </c>
       <c r="H129" s="16">
-        <v>0.0031603791954</v>
+        <v>0.0033764931356</v>
       </c>
       <c r="I129" s="15" t="s">
         <v>13</v>
@@ -5687,16 +5681,16 @@
         <v>13</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F130" s="14">
-        <v>28890</v>
+        <v>26328</v>
       </c>
       <c r="G130" s="15">
-        <v>125.17</v>
+        <v>153.81</v>
       </c>
       <c r="H130" s="16">
-        <v>0.0029611846986</v>
+        <v>0.0033034693034</v>
       </c>
       <c r="I130" s="15" t="s">
         <v>13</v>
@@ -5716,16 +5710,16 @@
         <v>13</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="F131" s="14">
-        <v>222745</v>
+        <v>13407</v>
       </c>
       <c r="G131" s="15">
-        <v>125.03</v>
+        <v>151.03</v>
       </c>
       <c r="H131" s="16">
-        <v>0.0029578726761</v>
+        <v>0.0032437615818</v>
       </c>
       <c r="I131" s="15" t="s">
         <v>13</v>
@@ -5745,16 +5739,16 @@
         <v>13</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="F132" s="14">
-        <v>3058</v>
+        <v>4429</v>
       </c>
       <c r="G132" s="15">
-        <v>123.66</v>
+        <v>147.12</v>
       </c>
       <c r="H132" s="16">
-        <v>0.0029254621701</v>
+        <v>0.0031597841748</v>
       </c>
       <c r="I132" s="15" t="s">
         <v>13</v>
@@ -5774,16 +5768,16 @@
         <v>13</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="F133" s="14">
-        <v>13191</v>
+        <v>30123</v>
       </c>
       <c r="G133" s="15">
-        <v>122.94</v>
+        <v>143.88</v>
       </c>
       <c r="H133" s="16">
-        <v>0.0029084289115</v>
+        <v>0.0030901967582</v>
       </c>
       <c r="I133" s="15" t="s">
         <v>13</v>
@@ -5803,16 +5797,16 @@
         <v>13</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="F134" s="14">
-        <v>38326</v>
+        <v>5620</v>
       </c>
       <c r="G134" s="15">
-        <v>118.96</v>
+        <v>141.11</v>
       </c>
       <c r="H134" s="16">
-        <v>0.0028142728429</v>
+        <v>0.0030307038125</v>
       </c>
       <c r="I134" s="15" t="s">
         <v>13</v>
@@ -5832,16 +5826,16 @@
         <v>13</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="F135" s="14">
-        <v>6074</v>
+        <v>264915</v>
       </c>
       <c r="G135" s="15">
-        <v>117.07</v>
+        <v>135.82</v>
       </c>
       <c r="H135" s="16">
-        <v>0.002769560539</v>
+        <v>0.0029170873207</v>
       </c>
       <c r="I135" s="15" t="s">
         <v>13</v>
@@ -5861,16 +5855,16 @@
         <v>13</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>214</v>
+        <v>23</v>
       </c>
       <c r="F136" s="14">
-        <v>289</v>
+        <v>11116</v>
       </c>
       <c r="G136" s="15">
-        <v>116.96</v>
+        <v>132.08</v>
       </c>
       <c r="H136" s="16">
-        <v>0.0027669582356</v>
+        <v>0.0028367611052</v>
       </c>
       <c r="I136" s="15" t="s">
         <v>13</v>
@@ -5890,16 +5884,16 @@
         <v>13</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="F137" s="14">
-        <v>10917</v>
+        <v>226441</v>
       </c>
       <c r="G137" s="15">
-        <v>113.49</v>
+        <v>131.06</v>
       </c>
       <c r="H137" s="16">
-        <v>0.0026848673919</v>
+        <v>0.0028148539556</v>
       </c>
       <c r="I137" s="15" t="s">
         <v>13</v>
@@ -5919,16 +5913,16 @@
         <v>13</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>314</v>
+        <v>125</v>
       </c>
       <c r="F138" s="14">
-        <v>371</v>
+        <v>99733</v>
       </c>
       <c r="G138" s="15">
-        <v>110.90</v>
+        <v>124.33</v>
       </c>
       <c r="H138" s="16">
-        <v>0.0026235949754</v>
+        <v>0.002670309723</v>
       </c>
       <c r="I138" s="15" t="s">
         <v>13</v>
@@ -5939,25 +5933,25 @@
     </row>
     <row r="139" spans="2:10" ht="15" customHeight="1">
       <c r="B139" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C139" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="C139" s="13" t="s">
-        <v>316</v>
-      </c>
       <c r="D139" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="F139" s="14">
-        <v>22654</v>
+        <v>44032</v>
       </c>
       <c r="G139" s="15">
-        <v>110.10</v>
+        <v>121.09</v>
       </c>
       <c r="H139" s="16">
-        <v>0.0026046691325</v>
+        <v>0.0026007223064</v>
       </c>
       <c r="I139" s="15" t="s">
         <v>13</v>
@@ -5968,25 +5962,25 @@
     </row>
     <row r="140" spans="2:10" ht="15" customHeight="1">
       <c r="B140" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="C140" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="C140" s="13" t="s">
-        <v>318</v>
-      </c>
       <c r="D140" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="F140" s="14">
-        <v>5437</v>
+        <v>1732</v>
       </c>
       <c r="G140" s="15">
-        <v>107.50</v>
+        <v>116.55</v>
       </c>
       <c r="H140" s="16">
-        <v>0.002543160143</v>
+        <v>0.0025032140128</v>
       </c>
       <c r="I140" s="15" t="s">
         <v>13</v>
@@ -5997,25 +5991,25 @@
     </row>
     <row r="141" spans="2:10" ht="15" customHeight="1">
       <c r="B141" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="C141" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="C141" s="13" t="s">
-        <v>320</v>
-      </c>
       <c r="D141" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="F141" s="14">
-        <v>206653</v>
+        <v>4706</v>
       </c>
       <c r="G141" s="15">
-        <v>105.99</v>
+        <v>114.44</v>
       </c>
       <c r="H141" s="16">
-        <v>0.0025074376145</v>
+        <v>0.0024578962817</v>
       </c>
       <c r="I141" s="15" t="s">
         <v>13</v>
@@ -6026,25 +6020,25 @@
     </row>
     <row r="142" spans="2:10" ht="15" customHeight="1">
       <c r="B142" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="C142" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="C142" s="13" t="s">
-        <v>322</v>
-      </c>
       <c r="D142" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="F142" s="14">
-        <v>1740</v>
+        <v>210084</v>
       </c>
       <c r="G142" s="15">
-        <v>104.84</v>
+        <v>113.40</v>
       </c>
       <c r="H142" s="16">
-        <v>0.0024802317153</v>
+        <v>0.00243555958</v>
       </c>
       <c r="I142" s="15" t="s">
         <v>13</v>
@@ -6055,25 +6049,25 @@
     </row>
     <row r="143" spans="2:10" ht="15" customHeight="1">
       <c r="B143" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="C143" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="C143" s="13" t="s">
-        <v>324</v>
-      </c>
       <c r="D143" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>125</v>
+        <v>184</v>
       </c>
       <c r="F143" s="14">
-        <v>35519</v>
+        <v>294</v>
       </c>
       <c r="G143" s="15">
-        <v>97.68</v>
+        <v>113.28</v>
       </c>
       <c r="H143" s="16">
-        <v>0.0023108454211</v>
+        <v>0.0024329822683</v>
       </c>
       <c r="I143" s="15" t="s">
         <v>13</v>
@@ -6084,25 +6078,25 @@
     </row>
     <row r="144" spans="2:10" ht="15" customHeight="1">
       <c r="B144" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="C144" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="C144" s="13" t="s">
-        <v>326</v>
-      </c>
       <c r="D144" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="F144" s="14">
-        <v>42854</v>
+        <v>99489</v>
       </c>
       <c r="G144" s="15">
-        <v>95.10</v>
+        <v>110.69</v>
       </c>
       <c r="H144" s="16">
-        <v>0.0022498095777</v>
+        <v>0.0023773552903</v>
       </c>
       <c r="I144" s="15" t="s">
         <v>13</v>
@@ -6113,25 +6107,25 @@
     </row>
     <row r="145" spans="2:10" ht="15" customHeight="1">
       <c r="B145" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="C145" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="C145" s="13" t="s">
+      <c r="D145" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="D145" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E145" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="F145" s="14">
-        <v>4632</v>
+        <v>377</v>
       </c>
       <c r="G145" s="15">
-        <v>92.15</v>
+        <v>110.37</v>
       </c>
       <c r="H145" s="16">
-        <v>0.0021800205319</v>
+        <v>0.002370482459</v>
       </c>
       <c r="I145" s="15" t="s">
         <v>13</v>
@@ -6151,16 +6145,16 @@
         <v>13</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F146" s="14">
-        <v>93954</v>
+        <v>62574</v>
       </c>
       <c r="G146" s="15">
-        <v>91.61</v>
+        <v>106.97</v>
       </c>
       <c r="H146" s="16">
-        <v>0.0021672455879</v>
+        <v>0.0022974586268</v>
       </c>
       <c r="I146" s="15" t="s">
         <v>13</v>
@@ -6180,16 +6174,16 @@
         <v>13</v>
       </c>
       <c r="E147" s="13" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="F147" s="14">
-        <v>805</v>
+        <v>23020</v>
       </c>
       <c r="G147" s="15">
-        <v>88.82</v>
+        <v>105.90</v>
       </c>
       <c r="H147" s="16">
-        <v>0.0021012417107</v>
+        <v>0.0022744775972</v>
       </c>
       <c r="I147" s="15" t="s">
         <v>13</v>
@@ -6209,16 +6203,16 @@
         <v>13</v>
       </c>
       <c r="E148" s="13" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F148" s="14">
-        <v>1674</v>
+        <v>36269</v>
       </c>
       <c r="G148" s="15">
-        <v>85.64</v>
+        <v>105.49</v>
       </c>
       <c r="H148" s="16">
-        <v>0.0020260114851</v>
+        <v>0.0022656717822</v>
       </c>
       <c r="I148" s="15" t="s">
         <v>13</v>
@@ -6238,16 +6232,16 @@
         <v>13</v>
       </c>
       <c r="E149" s="13" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="F149" s="14">
-        <v>8182</v>
+        <v>43565</v>
       </c>
       <c r="G149" s="15">
-        <v>75.35</v>
+        <v>105.31</v>
       </c>
       <c r="H149" s="16">
-        <v>0.0017825778305</v>
+        <v>0.0022618058146</v>
       </c>
       <c r="I149" s="15" t="s">
         <v>13</v>
@@ -6267,16 +6261,16 @@
         <v>13</v>
       </c>
       <c r="E150" s="13" t="s">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="F150" s="14">
-        <v>8386</v>
+        <v>3518</v>
       </c>
       <c r="G150" s="15">
-        <v>74.68</v>
+        <v>104.80</v>
       </c>
       <c r="H150" s="16">
-        <v>0.001766727437</v>
+        <v>0.0022508522398</v>
       </c>
       <c r="I150" s="15" t="s">
         <v>13</v>
@@ -6296,16 +6290,16 @@
         <v>13</v>
       </c>
       <c r="E151" s="13" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="F151" s="14">
-        <v>11161</v>
+        <v>8280</v>
       </c>
       <c r="G151" s="15">
-        <v>69.07</v>
+        <v>98.09</v>
       </c>
       <c r="H151" s="16">
-        <v>0.0016340099635</v>
+        <v>0.0021067375591</v>
       </c>
       <c r="I151" s="15" t="s">
         <v>13</v>
@@ -6316,25 +6310,25 @@
     </row>
     <row r="152" spans="2:10" ht="15" customHeight="1">
       <c r="B152" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C152" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="C152" s="13" t="s">
-        <v>343</v>
-      </c>
       <c r="D152" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E152" s="13" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F152" s="14">
-        <v>73753</v>
+        <v>8802</v>
       </c>
       <c r="G152" s="15">
-        <v>59.83</v>
+        <v>93.44</v>
       </c>
       <c r="H152" s="16">
-        <v>0.0014154164777</v>
+        <v>0.0020068667298</v>
       </c>
       <c r="I152" s="15" t="s">
         <v>13</v>
@@ -6345,25 +6339,25 @@
     </row>
     <row r="153" spans="2:10" ht="15" customHeight="1">
       <c r="B153" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="C153" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="C153" s="13" t="s">
-        <v>345</v>
-      </c>
       <c r="D153" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E153" s="13" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="F153" s="14">
-        <v>4874</v>
+        <v>95513</v>
       </c>
       <c r="G153" s="15">
-        <v>57.75</v>
+        <v>91.98</v>
       </c>
       <c r="H153" s="16">
-        <v>0.0013662092861</v>
+        <v>0.0019755094371</v>
       </c>
       <c r="I153" s="15" t="s">
         <v>13</v>
@@ -6374,25 +6368,25 @@
     </row>
     <row r="154" spans="2:10" ht="15" customHeight="1">
       <c r="B154" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="C154" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="C154" s="13" t="s">
+      <c r="D154" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E154" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="D154" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E154" s="13" t="s">
-        <v>103</v>
-      </c>
       <c r="F154" s="14">
-        <v>31611</v>
+        <v>13193</v>
       </c>
       <c r="G154" s="15">
-        <v>57.48</v>
+        <v>83.07</v>
       </c>
       <c r="H154" s="16">
-        <v>0.0013598218141</v>
+        <v>0.0017841440416</v>
       </c>
       <c r="I154" s="15" t="s">
         <v>13</v>
@@ -6412,16 +6406,16 @@
         <v>13</v>
       </c>
       <c r="E155" s="13" t="s">
-        <v>69</v>
+        <v>350</v>
       </c>
       <c r="F155" s="14">
-        <v>20762</v>
+        <v>119124</v>
       </c>
       <c r="G155" s="15">
-        <v>55.36</v>
+        <v>60.71</v>
       </c>
       <c r="H155" s="16">
-        <v>0.0013096683304</v>
+        <v>0.0013039049568</v>
       </c>
       <c r="I155" s="15" t="s">
         <v>13</v>
@@ -6432,25 +6426,25 @@
     </row>
     <row r="156" spans="2:10" ht="15" customHeight="1">
       <c r="B156" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C156" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D156" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E156" s="13" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F156" s="14">
-        <v>90104</v>
+        <v>32135</v>
       </c>
       <c r="G156" s="15">
-        <v>45.95</v>
+        <v>59.92</v>
       </c>
       <c r="H156" s="16">
-        <v>0.001087053103</v>
+        <v>0.0012869376546</v>
       </c>
       <c r="I156" s="15" t="s">
         <v>13</v>
@@ -6461,25 +6455,25 @@
     </row>
     <row r="157" spans="2:10" ht="15" customHeight="1">
       <c r="B157" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C157" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D157" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E157" s="13" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="F157" s="14">
-        <v>24071</v>
+        <v>62676</v>
       </c>
       <c r="G157" s="15">
-        <v>31.17</v>
+        <v>53.81</v>
       </c>
       <c r="H157" s="16">
-        <v>0.0007373981549</v>
+        <v>0.0011557095326</v>
       </c>
       <c r="I157" s="15" t="s">
         <v>13</v>
@@ -6490,6 +6484,27 @@
     </row>
     <row r="158" spans="2:10" ht="15" customHeight="1">
       <c r="B158" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C158" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="D158" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E158" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F158" s="14">
+        <v>23838</v>
+      </c>
+      <c r="G158" s="15">
+        <v>34.34</v>
+      </c>
+      <c r="H158" s="16">
+        <v>0.0007375407052</v>
+      </c>
+      <c r="I158" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J158" s="11" t="s">
@@ -6497,28 +6512,7 @@
       </c>
     </row>
     <row r="159" spans="2:10" ht="15" customHeight="1">
-      <c r="B159" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="C159" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D159" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E159" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F159" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G159" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H159" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I159" s="9" t="s">
+      <c r="B159" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J159" s="11" t="s">
@@ -6526,7 +6520,28 @@
       </c>
     </row>
     <row r="160" spans="2:10" ht="15" customHeight="1">
-      <c r="B160" s="12" t="s">
+      <c r="B160" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D160" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G160" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H160" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I160" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J160" s="11" t="s">
@@ -6534,28 +6549,7 @@
       </c>
     </row>
     <row r="161" spans="2:10" ht="15" customHeight="1">
-      <c r="B161" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C161" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D161" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E161" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F161" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G161" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H161" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I161" s="9" t="s">
+      <c r="B161" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J161" s="11" t="s">
@@ -6563,7 +6557,28 @@
       </c>
     </row>
     <row r="162" spans="2:10" ht="15" customHeight="1">
-      <c r="B162" s="12" t="s">
+      <c r="B162" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D162" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H162" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I162" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J162" s="11" t="s">
@@ -6571,36 +6586,36 @@
       </c>
     </row>
     <row r="163" spans="2:10" ht="15" customHeight="1">
-      <c r="B163" s="7" t="s">
+      <c r="B163" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J163" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164" spans="2:10" ht="15" customHeight="1">
+      <c r="B164" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C163" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D163" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E163" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F163" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G163" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H163" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I163" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J163" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="164" spans="2:10" ht="15" customHeight="1">
-      <c r="B164" s="12" t="s">
+      <c r="C164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H164" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I164" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J164" s="11" t="s">
@@ -6608,28 +6623,7 @@
       </c>
     </row>
     <row r="165" spans="2:10" ht="15" customHeight="1">
-      <c r="B165" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="C165" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D165" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E165" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F165" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G165" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H165" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I165" s="9" t="s">
+      <c r="B165" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J165" s="11" t="s">
@@ -6637,7 +6631,28 @@
       </c>
     </row>
     <row r="166" spans="2:10" ht="15" customHeight="1">
-      <c r="B166" s="12" t="s">
+      <c r="B166" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D166" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F166" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H166" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I166" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J166" s="11" t="s">
@@ -6645,36 +6660,36 @@
       </c>
     </row>
     <row r="167" spans="2:10" ht="15" customHeight="1">
-      <c r="B167" s="7" t="s">
+      <c r="B167" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J167" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168" spans="2:10" ht="15" customHeight="1">
+      <c r="B168" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E168" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F168" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G168" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="C167" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D167" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E167" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F167" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G167" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H167" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I167" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J167" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="168" spans="2:10" ht="15" customHeight="1">
-      <c r="B168" s="12" t="s">
+      <c r="H168" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I168" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J168" s="11" t="s">
@@ -6682,28 +6697,7 @@
       </c>
     </row>
     <row r="169" spans="2:10" ht="15" customHeight="1">
-      <c r="B169" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="C169" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D169" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E169" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F169" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G169" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H169" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I169" s="9" t="s">
+      <c r="B169" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J169" s="11" t="s">
@@ -6711,7 +6705,28 @@
       </c>
     </row>
     <row r="170" spans="2:10" ht="15" customHeight="1">
-      <c r="B170" s="12" t="s">
+      <c r="B170" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D170" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F170" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G170" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H170" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I170" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J170" s="11" t="s">
@@ -6719,28 +6734,7 @@
       </c>
     </row>
     <row r="171" spans="2:10" ht="15" customHeight="1">
-      <c r="B171" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="C171" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D171" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E171" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F171" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G171" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H171" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I171" s="9" t="s">
+      <c r="B171" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J171" s="11" t="s">
@@ -6748,7 +6742,28 @@
       </c>
     </row>
     <row r="172" spans="2:10" ht="15" customHeight="1">
-      <c r="B172" s="12" t="s">
+      <c r="B172" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D172" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E172" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G172" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H172" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I172" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J172" s="11" t="s">
@@ -6756,28 +6771,7 @@
       </c>
     </row>
     <row r="173" spans="2:10" ht="15" customHeight="1">
-      <c r="B173" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="C173" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D173" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E173" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F173" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G173" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H173" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I173" s="9" t="s">
+      <c r="B173" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J173" s="11" t="s">
@@ -6785,7 +6779,28 @@
       </c>
     </row>
     <row r="174" spans="2:10" ht="15" customHeight="1">
-      <c r="B174" s="12" t="s">
+      <c r="B174" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D174" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F174" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G174" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H174" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I174" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J174" s="11" t="s">
@@ -6793,28 +6808,7 @@
       </c>
     </row>
     <row r="175" spans="2:10" ht="15" customHeight="1">
-      <c r="B175" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="C175" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D175" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E175" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F175" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G175" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H175" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I175" s="9" t="s">
+      <c r="B175" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J175" s="11" t="s">
@@ -6822,7 +6816,28 @@
       </c>
     </row>
     <row r="176" spans="2:10" ht="15" customHeight="1">
-      <c r="B176" s="12" t="s">
+      <c r="B176" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D176" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F176" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G176" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H176" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I176" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J176" s="11" t="s">
@@ -6830,28 +6845,7 @@
       </c>
     </row>
     <row r="177" spans="2:10" ht="15" customHeight="1">
-      <c r="B177" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="C177" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D177" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E177" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F177" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G177" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H177" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I177" s="9" t="s">
+      <c r="B177" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J177" s="11" t="s">
@@ -6859,7 +6853,28 @@
       </c>
     </row>
     <row r="178" spans="2:10" ht="15" customHeight="1">
-      <c r="B178" s="12" t="s">
+      <c r="B178" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D178" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F178" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G178" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H178" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I178" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J178" s="11" t="s">
@@ -6867,28 +6882,7 @@
       </c>
     </row>
     <row r="179" spans="2:10" ht="15" customHeight="1">
-      <c r="B179" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="C179" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D179" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E179" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F179" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G179" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H179" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I179" s="9" t="s">
+      <c r="B179" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J179" s="11" t="s">
@@ -6896,7 +6890,28 @@
       </c>
     </row>
     <row r="180" spans="2:10" ht="15" customHeight="1">
-      <c r="B180" s="12" t="s">
+      <c r="B180" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D180" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F180" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G180" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H180" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I180" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J180" s="11" t="s">
@@ -6904,28 +6919,7 @@
       </c>
     </row>
     <row r="181" spans="2:10" ht="15" customHeight="1">
-      <c r="B181" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="C181" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D181" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E181" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F181" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G181" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H181" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I181" s="9" t="s">
+      <c r="B181" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J181" s="11" t="s">
@@ -6933,7 +6927,28 @@
       </c>
     </row>
     <row r="182" spans="2:10" ht="15" customHeight="1">
-      <c r="B182" s="12" t="s">
+      <c r="B182" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D182" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F182" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G182" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H182" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I182" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J182" s="11" t="s">
@@ -6941,28 +6956,7 @@
       </c>
     </row>
     <row r="183" spans="2:10" ht="15" customHeight="1">
-      <c r="B183" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="C183" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D183" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E183" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F183" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G183" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H183" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I183" s="9" t="s">
+      <c r="B183" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J183" s="11" t="s">
@@ -6970,7 +6964,28 @@
       </c>
     </row>
     <row r="184" spans="2:10" ht="15" customHeight="1">
-      <c r="B184" s="12" t="s">
+      <c r="B184" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D184" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F184" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G184" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H184" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I184" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J184" s="11" t="s">
@@ -6978,28 +6993,7 @@
       </c>
     </row>
     <row r="185" spans="2:10" ht="15" customHeight="1">
-      <c r="B185" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C185" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D185" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E185" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F185" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G185" s="9">
-        <v>8.98</v>
-      </c>
-      <c r="H185" s="10">
-        <v>0.0002124425868</v>
-      </c>
-      <c r="I185" s="9" t="s">
+      <c r="B185" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J185" s="11" t="s">
@@ -7007,7 +7001,28 @@
       </c>
     </row>
     <row r="186" spans="2:10" ht="15" customHeight="1">
-      <c r="B186" s="12" t="s">
+      <c r="B186" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D186" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F186" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G186" s="9">
+        <v>2.03</v>
+      </c>
+      <c r="H186" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="I186" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J186" s="11" t="s">
@@ -7015,37 +7030,16 @@
       </c>
     </row>
     <row r="187" spans="2:10" ht="15" customHeight="1">
-      <c r="B187" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="C187" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D187" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E187" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F187" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G187" s="18">
-        <v>-3.0059126999840373</v>
-      </c>
-      <c r="H187" s="19">
-        <v>-0.00007111178950790959</v>
-      </c>
-      <c r="I187" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J187" s="20" t="s">
+      <c r="B187" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J187" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="188" spans="2:10" ht="15" customHeight="1">
       <c r="B188" s="17" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C188" s="18" t="s">
         <v>13</v>
@@ -7060,10 +7054,10 @@
         <v>13</v>
       </c>
       <c r="G188" s="18">
-        <v>42270.2440873</v>
+        <v>25.32204170001205</v>
       </c>
       <c r="H188" s="19">
-        <v>0.9999999999926924</v>
+        <v>0.0005438566247786193</v>
       </c>
       <c r="I188" s="18" t="s">
         <v>13</v>
@@ -7072,181 +7066,169 @@
         <v>13</v>
       </c>
     </row>
-    <row r="190" spans="2:3" ht="15" customHeight="1">
-      <c r="B190" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="C190" s="22"/>
+    <row r="189" spans="2:10" ht="15" customHeight="1">
+      <c r="B189" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="C189" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D189" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E189" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G189" s="18">
+        <v>46560.1420417</v>
+      </c>
+      <c r="H189" s="19">
+        <v>0.9999999999918785</v>
+      </c>
+      <c r="I189" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J189" s="20" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="191" spans="2:3" ht="15" customHeight="1">
-      <c r="B191" s="23" t="s">
-        <v>371</v>
-      </c>
-      <c r="C191" s="24" t="s">
+      <c r="B191" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="C191" s="22"/>
+    </row>
+    <row r="192" spans="2:3" ht="15" customHeight="1">
+      <c r="B192" s="23" t="s">
+        <v>375</v>
+      </c>
+      <c r="C192" s="24" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="192" spans="2:3" ht="15" customHeight="1">
-      <c r="B192" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C192" s="26">
-        <v>37000</v>
       </c>
     </row>
     <row r="193" spans="2:3" ht="15" customHeight="1">
       <c r="B193" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C193" s="26">
-        <v>1000</v>
+        <v>376</v>
+      </c>
+      <c r="C193" s="25">
+        <v>54000</v>
       </c>
     </row>
     <row r="194" spans="2:3" ht="15" customHeight="1">
       <c r="B194" s="25" t="s">
-        <v>372</v>
-      </c>
-      <c r="C194" s="26">
-        <v>9828</v>
+        <v>294</v>
+      </c>
+      <c r="C194" s="25">
+        <v>17000</v>
       </c>
     </row>
     <row r="195" spans="2:3" ht="15" customHeight="1">
       <c r="B195" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="C195" s="26">
-        <v>1600</v>
+        <v>252</v>
+      </c>
+      <c r="C195" s="25">
+        <v>15000</v>
       </c>
     </row>
     <row r="196" spans="2:3" ht="15" customHeight="1">
       <c r="B196" s="25" t="s">
-        <v>374</v>
-      </c>
-      <c r="C196" s="26">
+        <v>377</v>
+      </c>
+      <c r="C196" s="25">
         <v>20000</v>
       </c>
     </row>
-    <row r="197" spans="2:3" ht="15" customHeight="1">
-      <c r="B197" s="25" t="s">
-        <v>375</v>
-      </c>
-      <c r="C197" s="26">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="198" spans="2:3" ht="15" customHeight="1">
-      <c r="B198" s="25" t="s">
-        <v>376</v>
-      </c>
-      <c r="C198" s="26">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="199" spans="2:3" ht="15" customHeight="1">
-      <c r="B199" s="25" t="s">
-        <v>377</v>
-      </c>
-      <c r="C199" s="26">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="200" spans="2:3" ht="15" customHeight="1">
-      <c r="B200" s="25" t="s">
+    <row r="198" spans="2:9" ht="15" customHeight="1">
+      <c r="B198" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="C200" s="26">
-        <v>7800</v>
-      </c>
-    </row>
-    <row r="201" spans="2:3" ht="15" customHeight="1">
-      <c r="B201" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="C201" s="26">
-        <v>5800</v>
-      </c>
-    </row>
-    <row r="203" spans="2:9" ht="15" customHeight="1">
-      <c r="B203" s="13" t="s">
+      <c r="C198" s="26"/>
+      <c r="D198" s="26"/>
+      <c r="E198" s="26"/>
+      <c r="F198" s="26"/>
+      <c r="G198" s="26"/>
+      <c r="H198" s="26"/>
+      <c r="I198" s="26"/>
+    </row>
+    <row r="199" spans="2:8" ht="15" customHeight="1">
+      <c r="B199" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="C203" s="27"/>
-      <c r="D203" s="27"/>
-      <c r="E203" s="27"/>
-      <c r="F203" s="27"/>
-      <c r="G203" s="27"/>
-      <c r="H203" s="27"/>
-      <c r="I203" s="27"/>
-    </row>
-    <row r="204" spans="2:8" ht="15" customHeight="1">
-      <c r="B204" s="13" t="s">
+      <c r="C199" s="26"/>
+      <c r="D199" s="26"/>
+      <c r="E199" s="26"/>
+      <c r="F199" s="26"/>
+      <c r="G199" s="26"/>
+      <c r="H199" s="26"/>
+    </row>
+    <row r="200" spans="2:8" ht="15" customHeight="1">
+      <c r="B200" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="C204" s="27"/>
-      <c r="D204" s="27"/>
-      <c r="E204" s="27"/>
-      <c r="F204" s="27"/>
-      <c r="G204" s="27"/>
-      <c r="H204" s="27"/>
-    </row>
-    <row r="205" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B205" s="28" t="s">
+      <c r="C200" s="26"/>
+      <c r="D200" s="26"/>
+      <c r="E200" s="26"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="26"/>
+      <c r="H200" s="26"/>
+    </row>
+    <row r="201" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B201" s="27" t="s">
         <v>381</v>
       </c>
-      <c r="C205" s="27"/>
-      <c r="D205" s="27"/>
-      <c r="E205" s="27"/>
-      <c r="F205" s="27"/>
-      <c r="G205" s="27"/>
-      <c r="H205" s="27"/>
-    </row>
-    <row r="206" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B206" s="28" t="s">
+      <c r="C201" s="26"/>
+      <c r="D201" s="26"/>
+      <c r="E201" s="26"/>
+      <c r="F201" s="26"/>
+      <c r="G201" s="26"/>
+      <c r="H201" s="26"/>
+    </row>
+    <row r="202" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B202" s="27" t="s">
         <v>382</v>
       </c>
-      <c r="C206" s="27"/>
-      <c r="D206" s="27"/>
-      <c r="E206" s="27"/>
-      <c r="F206" s="27"/>
-      <c r="G206" s="27"/>
-      <c r="H206" s="27"/>
-    </row>
-    <row r="207" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B207" s="28" t="s">
+      <c r="C202" s="26"/>
+      <c r="D202" s="26"/>
+      <c r="E202" s="26"/>
+      <c r="F202" s="26"/>
+      <c r="G202" s="26"/>
+      <c r="H202" s="26"/>
+    </row>
+    <row r="203" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B203" s="27" t="s">
         <v>383</v>
       </c>
-      <c r="C207" s="27"/>
-      <c r="D207" s="27"/>
-      <c r="E207" s="27"/>
-      <c r="F207" s="27"/>
-      <c r="G207" s="27"/>
-      <c r="H207" s="27"/>
-    </row>
-    <row r="210" ht="15">
-      <c r="B210" s="27" t="s">
+      <c r="C203" s="26"/>
+      <c r="D203" s="26"/>
+      <c r="E203" s="26"/>
+      <c r="F203" s="26"/>
+      <c r="G203" s="26"/>
+      <c r="H203" s="26"/>
+    </row>
+    <row r="206" ht="15">
+      <c r="B206" s="26" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="225" ht="15">
-      <c r="B225" s="27" t="s">
+    <row r="221" ht="15">
+      <c r="B221" s="26" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="226" ht="15">
-      <c r="B226" s="27" t="s">
-        <v>386</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B205:H205"/>
-    <mergeCell ref="B206:H206"/>
-    <mergeCell ref="B207:H207"/>
+  <mergeCells count="9">
+    <mergeCell ref="B200:H200"/>
+    <mergeCell ref="B201:H201"/>
+    <mergeCell ref="B202:H202"/>
+    <mergeCell ref="B203:H203"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B203:I203"/>
-    <mergeCell ref="B204:H204"/>
+    <mergeCell ref="B198:I198"/>
+    <mergeCell ref="B199:H199"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
